--- a/docs/downloads/indices/nifty-alpha-50.xlsx
+++ b/docs/downloads/indices/nifty-alpha-50.xlsx
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>56192.35</v>
+        <v>55808.95</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>23.48</v>
+        <v>23.32</v>
       </c>
     </row>
     <row r="6">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>2393.200596252129</v>
+        <v>2393.179674099485</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1.059572407848715</v>
+        <v>1.059621562802822</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04258943781942078</v>
+        <v>0.04288164665523156</v>
       </c>
     </row>
     <row r="8">
@@ -720,10 +720,10 @@
         <v>29.75</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>71197.71773850084</v>
+        <v>71197.09530445967</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>0.2670357751277681</v>
+        <v>0.2757289879931386</v>
       </c>
     </row>
     <row r="14">
@@ -736,10 +736,10 @@
         <v>41.96</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>100418.6970187393</v>
+        <v>100417.8191252144</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.787052810902896</v>
+        <v>0.799313893653516</v>
       </c>
     </row>
     <row r="15"/>
@@ -4197,7 +4197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4288,6 +4288,39 @@
       </c>
       <c r="I2">
         <f>IF(H2="","",IF(H2&gt;=70,"BUY",IF(H2&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>55808.95</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>23.32</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>0.1953125</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>1.0596215628</v>
+      </c>
+      <c r="F3" s="22">
+        <f>IF(D3="","",100*(1-D3))</f>
+        <v/>
+      </c>
+      <c r="G3" s="22">
+        <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H3" s="22">
+        <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
+        <v/>
+      </c>
+      <c r="I3">
+        <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-alpha-50.xlsx
+++ b/docs/downloads/indices/nifty-alpha-50.xlsx
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>55808.95</v>
+        <v>55466.15</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>23.32</v>
+        <v>23.18</v>
       </c>
     </row>
     <row r="6">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>2393.179674099485</v>
+        <v>2392.845125107852</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1.059621562802822</v>
+        <v>1.059324235722265</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04288164665523156</v>
+        <v>0.04314063848144953</v>
       </c>
     </row>
     <row r="8">
@@ -720,10 +720,10 @@
         <v>29.75</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>71197.09530445967</v>
+        <v>71187.14247195858</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>0.2757289879931386</v>
+        <v>0.2834339948231233</v>
       </c>
     </row>
     <row r="14">
@@ -736,10 +736,10 @@
         <v>41.96</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>100417.8191252144</v>
+        <v>100403.7814495255</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.799313893653516</v>
+        <v>0.8101811906816221</v>
       </c>
     </row>
     <row r="15"/>
@@ -4197,7 +4197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4321,6 +4321,39 @@
       </c>
       <c r="I3">
         <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>55466.15</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>23.18</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>0.1953125</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>1.05932423572</v>
+      </c>
+      <c r="F4" s="22">
+        <f>IF(D4="","",100*(1-D4))</f>
+        <v/>
+      </c>
+      <c r="G4" s="22">
+        <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H4" s="22">
+        <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
+        <v/>
+      </c>
+      <c r="I4">
+        <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-alpha-50.xlsx
+++ b/docs/downloads/indices/nifty-alpha-50.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Quarterly Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Score History" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Composition" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,17 +21,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="dd-mmm-yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00;[Red](#,##0.00);-"/>
-    <numFmt numFmtId="167" formatCode="0.00x;[Red](0.00x);-"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0;[Red](#,##0.0);-"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="0.00x"/>
+  <numFmts count="7">
+    <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00;[Red](#,##0.00);-"/>
+    <numFmt numFmtId="166" formatCode="0.00x;[Red](0.00x);-"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0;[Red](#,##0.0);-"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,6 +67,11 @@
       <color theme="10"/>
       <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
     </font>
   </fonts>
   <fills count="5">
@@ -105,36 +110,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -566,7 +584,7 @@
           <t>As of</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="23" t="n">
         <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -580,7 +598,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -594,7 +611,7 @@
           <t>Index level</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>55466.15</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -602,7 +619,7 @@
           <t>P/E</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="25" t="n">
         <v>23.18</v>
       </c>
     </row>
@@ -612,7 +629,7 @@
           <t>P/E percentile</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="26" t="n">
         <v>0.1953125</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -620,7 +637,7 @@
           <t>Implied EPS</t>
         </is>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="27" t="n">
         <v>2392.845125107852</v>
       </c>
     </row>
@@ -630,7 +647,7 @@
           <t>YoY implied EPS growth</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="26" t="n">
         <v>1.059324235722265</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -648,7 +665,7 @@
           <t>Valuation score</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="28" t="n">
         <v>80.46875</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -656,7 +673,7 @@
           <t>Growth score</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="28" t="n">
         <v>100</v>
       </c>
     </row>
@@ -666,7 +683,7 @@
           <t>Composite score</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="28" t="n">
         <v>86.328125</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -680,7 +697,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -716,13 +732,13 @@
           <t>BUY → HOLD</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="29" t="n">
         <v>29.75</v>
       </c>
       <c r="C13" s="15" t="n">
         <v>71187.14247195858</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="30" t="n">
         <v>0.2834339948231233</v>
       </c>
     </row>
@@ -732,17 +748,16 @@
           <t>HOLD → SELL</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="29" t="n">
         <v>41.96</v>
       </c>
       <c r="C14" s="15" t="n">
         <v>100403.7814495255</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="30" t="n">
         <v>0.8101811906816221</v>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
@@ -796,17 +811,17 @@
       <c r="B18" t="n">
         <v>7</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="30" t="n">
         <v>0.6552149306854191</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="30" t="n">
         <v>0.1724472302215659</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="30" t="n">
         <v>0.268370171373254</v>
       </c>
-      <c r="F18" s="16" t="n"/>
-      <c r="G18" s="16" t="n">
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n">
         <v>0.1666666666666667</v>
       </c>
     </row>
@@ -819,17 +834,17 @@
       <c r="B19" t="n">
         <v>8</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="30" t="n">
         <v>0.1822736973034699</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="30" t="n">
         <v>0.3689030548818619</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="30" t="n">
         <v>0.2777889235479469</v>
       </c>
-      <c r="F19" s="16" t="n"/>
-      <c r="G19" s="16" t="n">
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -842,19 +857,19 @@
       <c r="B20" t="n">
         <v>8</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="30" t="n">
         <v>0.193638156564597</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="30" t="n">
         <v>0.2764956332058897</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="30" t="n">
         <v>0.2975018278699266</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="F20" s="30" t="n">
         <v>0.1998241211570164</v>
       </c>
-      <c r="G20" s="16" t="n">
+      <c r="G20" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -867,19 +882,19 @@
       <c r="B21" t="n">
         <v>8</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="30" t="n">
         <v>-0.03296630441988901</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="30" t="n">
         <v>0.2624408626493824</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="30" t="n">
         <v>0.3130642510298619</v>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="F21" s="30" t="n">
         <v>0.1783410127390987</v>
       </c>
-      <c r="G21" s="16" t="n">
+      <c r="G21" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -892,23 +907,22 @@
       <c r="B22" t="n">
         <v>9</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="30" t="n">
         <v>-0.03393771881334073</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="30" t="n">
         <v>0.1486383644881587</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="30" t="n">
         <v>0.1579770546344743</v>
       </c>
-      <c r="F22" s="16" t="n">
+      <c r="F22" s="30" t="n">
         <v>0.1813554528289574</v>
       </c>
-      <c r="G22" s="16" t="n">
+      <c r="G22" s="30" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
@@ -1044,14 +1058,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>44316</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>24547.7</v>
       </c>
-      <c r="C2" s="7" t="n"/>
-      <c r="D2" s="19">
+      <c r="C2" s="25" t="n"/>
+      <c r="D2" s="32">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
@@ -1061,14 +1075,14 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>44347</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>26292.35</v>
       </c>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="19">
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="32">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
@@ -1078,16 +1092,16 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>27135</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>55.12</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="32">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
@@ -1097,16 +1111,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>44408</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>28513.05</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>52.19</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="32">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
@@ -1116,16 +1130,16 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>44439</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>30213.4</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>41.25</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="32">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
@@ -1135,16 +1149,16 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>31641.8</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>36.37</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="32">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
@@ -1154,16 +1168,16 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>44500</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>31388.8</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>34.84</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="32">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
@@ -1173,16 +1187,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>44530</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>32234.85</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>30.85</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="32">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
@@ -1192,16 +1206,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>34605.05</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>35.34</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="32">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
@@ -1211,16 +1225,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>44592</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>33759.45</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>33.66</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="32">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
@@ -1230,16 +1244,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>44620</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>31885.3</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>30.72</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="32">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
@@ -1249,16 +1263,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>35463.05</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>31.75</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="32">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
@@ -1268,16 +1282,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>44681</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>34333.15</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>30.2</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="32">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
@@ -1287,16 +1301,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>44712</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>30173.5</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>24.36</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="32">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
@@ -1306,16 +1320,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>26214.1</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>29.75</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="32">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
@@ -1325,16 +1339,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>44773</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>28286.15</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>31.2</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="32">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
@@ -1344,16 +1358,16 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>44804</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>29957.6</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>25.36</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="32">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
@@ -1363,16 +1377,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>29586.2</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>41.96</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="32">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
@@ -1382,16 +1396,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44865</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>30520.5</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>41.44</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="32">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
@@ -1401,16 +1415,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44895</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>30688.1</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>38.55</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="32">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
@@ -1420,16 +1434,16 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>29685.5</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>17.97</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="32">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
@@ -1439,16 +1453,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>44957</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>27358.05</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>15.93</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="32">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
@@ -1458,16 +1472,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>44985</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>25277.2</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>14.15</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="32">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
@@ -1477,16 +1491,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>25993.55</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>15.12</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="32">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
@@ -1496,16 +1510,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>45046</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>27659.4</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>16.12</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="32">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
@@ -1515,16 +1529,16 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>45077</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>29305.7</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>15.58</v>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="32">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
@@ -1534,16 +1548,16 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>31290.15</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>16.42</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="32">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
@@ -1553,16 +1567,16 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>45138</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>33995.7</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>16.84</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="32">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
@@ -1572,16 +1586,16 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>45169</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>34723.85</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>16.39</v>
       </c>
-      <c r="D30" s="19">
+      <c r="D30" s="32">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
@@ -1591,16 +1605,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>36496.65</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>16.04</v>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="32">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
@@ -1610,16 +1624,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45230</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>35216.15</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>14.89</v>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="32">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
@@ -1629,16 +1643,16 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45260</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>39097.85</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>16.44</v>
       </c>
-      <c r="D33" s="19">
+      <c r="D33" s="32">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
@@ -1648,16 +1662,16 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>42306.3</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>26.68</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="32">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
@@ -1667,16 +1681,16 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>45322</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>47075.2</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>27.97</v>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="32">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
@@ -1686,16 +1700,16 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>45351</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>46491.55</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>27.23</v>
       </c>
-      <c r="D36" s="19">
+      <c r="D36" s="32">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
@@ -1705,16 +1719,16 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="24" t="n">
         <v>47200.3</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="25" t="n">
         <v>27.39</v>
       </c>
-      <c r="D37" s="19">
+      <c r="D37" s="32">
         <f>IFERROR(B37/C37,"")</f>
         <v/>
       </c>
@@ -1724,16 +1738,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="31" t="n">
         <v>45412</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="24" t="n">
         <v>50494.7</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="25" t="n">
         <v>29.07</v>
       </c>
-      <c r="D38" s="19">
+      <c r="D38" s="32">
         <f>IFERROR(B38/C38,"")</f>
         <v/>
       </c>
@@ -1743,16 +1757,16 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="31" t="n">
         <v>45443</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="24" t="n">
         <v>53190.65</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="25" t="n">
         <v>29.95</v>
       </c>
-      <c r="D39" s="19">
+      <c r="D39" s="32">
         <f>IFERROR(B39/C39,"")</f>
         <v/>
       </c>
@@ -1762,16 +1776,16 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="24" t="n">
         <v>56314.8</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="25" t="n">
         <v>30.79</v>
       </c>
-      <c r="D40" s="19">
+      <c r="D40" s="32">
         <f>IFERROR(B40/C40,"")</f>
         <v/>
       </c>
@@ -1781,16 +1795,16 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="31" t="n">
         <v>45504</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="24" t="n">
         <v>60090.65</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="25" t="n">
         <v>31.66</v>
       </c>
-      <c r="D41" s="19">
+      <c r="D41" s="32">
         <f>IFERROR(B41/C41,"")</f>
         <v/>
       </c>
@@ -1800,16 +1814,16 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="31" t="n">
         <v>45535</v>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="24" t="n">
         <v>60274.95</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="25" t="n">
         <v>31.33</v>
       </c>
-      <c r="D42" s="19">
+      <c r="D42" s="32">
         <f>IFERROR(B42/C42,"")</f>
         <v/>
       </c>
@@ -1819,16 +1833,16 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n">
+      <c r="A43" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="24" t="n">
         <v>60409.8</v>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="25" t="n">
         <v>41.61</v>
       </c>
-      <c r="D43" s="19">
+      <c r="D43" s="32">
         <f>IFERROR(B43/C43,"")</f>
         <v/>
       </c>
@@ -1838,16 +1852,16 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="n">
+      <c r="A44" s="31" t="n">
         <v>45596</v>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" s="24" t="n">
         <v>56150.2</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="25" t="n">
         <v>39.48</v>
       </c>
-      <c r="D44" s="19">
+      <c r="D44" s="32">
         <f>IFERROR(B44/C44,"")</f>
         <v/>
       </c>
@@ -1857,16 +1871,16 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="n">
+      <c r="A45" s="31" t="n">
         <v>45626</v>
       </c>
-      <c r="B45" s="6" t="n">
+      <c r="B45" s="24" t="n">
         <v>56108.85</v>
       </c>
-      <c r="C45" s="7" t="n">
+      <c r="C45" s="25" t="n">
         <v>37.8</v>
       </c>
-      <c r="D45" s="19">
+      <c r="D45" s="32">
         <f>IFERROR(B45/C45,"")</f>
         <v/>
       </c>
@@ -1876,16 +1890,16 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="n">
+      <c r="A46" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B46" s="6" t="n">
+      <c r="B46" s="24" t="n">
         <v>56293.05</v>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C46" s="25" t="n">
         <v>42.38</v>
       </c>
-      <c r="D46" s="19">
+      <c r="D46" s="32">
         <f>IFERROR(B46/C46,"")</f>
         <v/>
       </c>
@@ -1895,16 +1909,16 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="n">
+      <c r="A47" s="31" t="n">
         <v>45688</v>
       </c>
-      <c r="B47" s="6" t="n">
+      <c r="B47" s="24" t="n">
         <v>49962.65</v>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C47" s="25" t="n">
         <v>36.28</v>
       </c>
-      <c r="D47" s="19">
+      <c r="D47" s="32">
         <f>IFERROR(B47/C47,"")</f>
         <v/>
       </c>
@@ -1914,16 +1928,16 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="n">
+      <c r="A48" s="31" t="n">
         <v>45716</v>
       </c>
-      <c r="B48" s="6" t="n">
+      <c r="B48" s="24" t="n">
         <v>42264.05</v>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C48" s="25" t="n">
         <v>29.46</v>
       </c>
-      <c r="D48" s="19">
+      <c r="D48" s="32">
         <f>IFERROR(B48/C48,"")</f>
         <v/>
       </c>
@@ -1933,16 +1947,16 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="n">
+      <c r="A49" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B49" s="6" t="n">
+      <c r="B49" s="24" t="n">
         <v>46004.55</v>
       </c>
-      <c r="C49" s="7" t="n">
+      <c r="C49" s="25" t="n">
         <v>41.36</v>
       </c>
-      <c r="D49" s="19">
+      <c r="D49" s="32">
         <f>IFERROR(B49/C49,"")</f>
         <v/>
       </c>
@@ -1952,16 +1966,16 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="n">
+      <c r="A50" s="31" t="n">
         <v>45777</v>
       </c>
-      <c r="B50" s="6" t="n">
+      <c r="B50" s="24" t="n">
         <v>47670.8</v>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C50" s="25" t="n">
         <v>43.68</v>
       </c>
-      <c r="D50" s="19">
+      <c r="D50" s="32">
         <f>IFERROR(B50/C50,"")</f>
         <v/>
       </c>
@@ -1971,16 +1985,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="n">
+      <c r="A51" s="31" t="n">
         <v>45808</v>
       </c>
-      <c r="B51" s="6" t="n">
+      <c r="B51" s="24" t="n">
         <v>51179.25</v>
       </c>
-      <c r="C51" s="7" t="n">
+      <c r="C51" s="25" t="n">
         <v>40.78</v>
       </c>
-      <c r="D51" s="19">
+      <c r="D51" s="32">
         <f>IFERROR(B51/C51,"")</f>
         <v/>
       </c>
@@ -1990,16 +2004,16 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="n">
+      <c r="A52" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B52" s="6" t="n">
+      <c r="B52" s="24" t="n">
         <v>53900.45</v>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C52" s="25" t="n">
         <v>51.51</v>
       </c>
-      <c r="D52" s="19">
+      <c r="D52" s="32">
         <f>IFERROR(B52/C52,"")</f>
         <v/>
       </c>
@@ -2009,16 +2023,16 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="n">
+      <c r="A53" s="31" t="n">
         <v>45869</v>
       </c>
-      <c r="B53" s="6" t="n">
+      <c r="B53" s="24" t="n">
         <v>52171</v>
       </c>
-      <c r="C53" s="7" t="n">
+      <c r="C53" s="25" t="n">
         <v>46.41</v>
       </c>
-      <c r="D53" s="19">
+      <c r="D53" s="32">
         <f>IFERROR(B53/C53,"")</f>
         <v/>
       </c>
@@ -2028,16 +2042,16 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="n">
+      <c r="A54" s="31" t="n">
         <v>45900</v>
       </c>
-      <c r="B54" s="6" t="n">
+      <c r="B54" s="24" t="n">
         <v>49066.25</v>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C54" s="25" t="n">
         <v>42.22</v>
       </c>
-      <c r="D54" s="19">
+      <c r="D54" s="32">
         <f>IFERROR(B54/C54,"")</f>
         <v/>
       </c>
@@ -2047,16 +2061,16 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="n">
+      <c r="A55" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B55" s="6" t="n">
+      <c r="B55" s="24" t="n">
         <v>48722.95</v>
       </c>
-      <c r="C55" s="7" t="n">
+      <c r="C55" s="25" t="n">
         <v>40.37</v>
       </c>
-      <c r="D55" s="19">
+      <c r="D55" s="32">
         <f>IFERROR(B55/C55,"")</f>
         <v/>
       </c>
@@ -2066,16 +2080,16 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="n">
+      <c r="A56" s="31" t="n">
         <v>45961</v>
       </c>
-      <c r="B56" s="6" t="n">
+      <c r="B56" s="24" t="n">
         <v>50867.3</v>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C56" s="25" t="n">
         <v>42.21</v>
       </c>
-      <c r="D56" s="19">
+      <c r="D56" s="32">
         <f>IFERROR(B56/C56,"")</f>
         <v/>
       </c>
@@ -2085,16 +2099,16 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="18" t="n">
+      <c r="A57" s="31" t="n">
         <v>45991</v>
       </c>
-      <c r="B57" s="6" t="n">
+      <c r="B57" s="24" t="n">
         <v>52105.25</v>
       </c>
-      <c r="C57" s="7" t="n">
+      <c r="C57" s="25" t="n">
         <v>51.63</v>
       </c>
-      <c r="D57" s="19">
+      <c r="D57" s="32">
         <f>IFERROR(B57/C57,"")</f>
         <v/>
       </c>
@@ -2104,16 +2118,16 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="18" t="n">
+      <c r="A58" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B58" s="6" t="n">
+      <c r="B58" s="24" t="n">
         <v>50309.15</v>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C58" s="25" t="n">
         <v>33.05</v>
       </c>
-      <c r="D58" s="19">
+      <c r="D58" s="32">
         <f>IFERROR(B58/C58,"")</f>
         <v/>
       </c>
@@ -2123,16 +2137,16 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="18" t="n">
+      <c r="A59" s="31" t="n">
         <v>46053</v>
       </c>
-      <c r="B59" s="6" t="n">
+      <c r="B59" s="24" t="n">
         <v>48636.85</v>
       </c>
-      <c r="C59" s="7" t="n">
+      <c r="C59" s="25" t="n">
         <v>31</v>
       </c>
-      <c r="D59" s="19">
+      <c r="D59" s="32">
         <f>IFERROR(B59/C59,"")</f>
         <v/>
       </c>
@@ -2142,16 +2156,16 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="n">
+      <c r="A60" s="31" t="n">
         <v>46081</v>
       </c>
-      <c r="B60" s="6" t="n">
+      <c r="B60" s="24" t="n">
         <v>50663.15</v>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C60" s="25" t="n">
         <v>31.48</v>
       </c>
-      <c r="D60" s="19">
+      <c r="D60" s="32">
         <f>IFERROR(B60/C60,"")</f>
         <v/>
       </c>
@@ -2161,16 +2175,16 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="18" t="n">
+      <c r="A61" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B61" s="6" t="n">
+      <c r="B61" s="24" t="n">
         <v>44487.95</v>
       </c>
-      <c r="C61" s="7" t="n">
+      <c r="C61" s="25" t="n">
         <v>23.91</v>
       </c>
-      <c r="D61" s="19">
+      <c r="D61" s="32">
         <f>IFERROR(B61/C61,"")</f>
         <v/>
       </c>
@@ -2180,16 +2194,16 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="18" t="n">
+      <c r="A62" s="31" t="n">
         <v>46142</v>
       </c>
-      <c r="B62" s="6" t="n">
+      <c r="B62" s="24" t="n">
         <v>50876.15</v>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C62" s="25" t="n">
         <v>27.02</v>
       </c>
-      <c r="D62" s="19">
+      <c r="D62" s="32">
         <f>IFERROR(B62/C62,"")</f>
         <v/>
       </c>
@@ -2199,16 +2213,16 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="18" t="n">
+      <c r="A63" s="31" t="n">
         <v>46173</v>
       </c>
-      <c r="B63" s="6" t="n">
+      <c r="B63" s="24" t="n">
         <v>52795.35</v>
       </c>
-      <c r="C63" s="7" t="n">
+      <c r="C63" s="25" t="n">
         <v>26.79</v>
       </c>
-      <c r="D63" s="19">
+      <c r="D63" s="32">
         <f>IFERROR(B63/C63,"")</f>
         <v/>
       </c>
@@ -2218,16 +2232,16 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="18" t="n">
+      <c r="A64" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B64" s="6" t="n">
+      <c r="B64" s="24" t="n">
         <v>53700.3</v>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C64" s="25" t="n">
         <v>24.79</v>
       </c>
-      <c r="D64" s="19">
+      <c r="D64" s="32">
         <f>IFERROR(B64/C64,"")</f>
         <v/>
       </c>
@@ -2237,16 +2251,16 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="18" t="n">
+      <c r="A65" s="31" t="n">
         <v>46234</v>
       </c>
-      <c r="B65" s="6" t="n">
+      <c r="B65" s="24" t="n">
         <v>54236.25</v>
       </c>
-      <c r="C65" s="7" t="n">
+      <c r="C65" s="25" t="n">
         <v>24.06</v>
       </c>
-      <c r="D65" s="19">
+      <c r="D65" s="32">
         <f>IFERROR(B65/C65,"")</f>
         <v/>
       </c>
@@ -2256,16 +2270,16 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="18" t="n">
+      <c r="A66" s="31" t="n">
         <v>46265</v>
       </c>
-      <c r="B66" s="6" t="n">
+      <c r="B66" s="24" t="n">
         <v>57539.1</v>
       </c>
-      <c r="C66" s="7" t="n">
+      <c r="C66" s="25" t="n">
         <v>24.05</v>
       </c>
-      <c r="D66" s="19">
+      <c r="D66" s="32">
         <f>IFERROR(B66/C66,"")</f>
         <v/>
       </c>
@@ -2367,13 +2381,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>42369</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>9502.57</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>45.37</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2381,12 +2395,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="33">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
-      <c r="F2" s="16" t="n"/>
-      <c r="G2" s="16">
+      <c r="F2" s="30" t="n"/>
+      <c r="G2" s="30">
         <f>IF(C2="","",(COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,C2)+1)/2)/COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2394,31 +2408,31 @@
         <f>IF(G2="","",IF(G2&lt;=20%,"Q1 Cheapest",IF(G2&lt;=40%,"Q2",IF(G2&lt;=60%,"Q3",IF(G2&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I2" s="16">
+      <c r="I2" s="30">
         <f>IFERROR(B6/B2-1,"")</f>
         <v/>
       </c>
-      <c r="J2" s="16">
+      <c r="J2" s="30">
         <f>IFERROR((B14/B2)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K2" s="16">
+      <c r="K2" s="30">
         <f>IFERROR((B22/B2)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L2" s="16">
+      <c r="L2" s="30">
         <f>IFERROR((B42/B2)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>42460</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>8620.5</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>42.71</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -2426,12 +2440,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="33">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
-      <c r="F3" s="16" t="n"/>
-      <c r="G3" s="16">
+      <c r="F3" s="30" t="n"/>
+      <c r="G3" s="30">
         <f>IF(C3="","",(COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,C3)+1)/2)/COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2439,31 +2453,31 @@
         <f>IF(G3="","",IF(G3&lt;=20%,"Q1 Cheapest",IF(G3&lt;=40%,"Q2",IF(G3&lt;=60%,"Q3",IF(G3&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="30">
         <f>IFERROR(B7/B3-1,"")</f>
         <v/>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="30">
         <f>IFERROR((B15/B3)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="30">
         <f>IFERROR((B23/B3)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="30">
         <f>IFERROR((B43/B3)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>42551</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>8685.620000000001</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>27.75</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2471,12 +2485,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="33">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
-      <c r="F4" s="16" t="n"/>
-      <c r="G4" s="16">
+      <c r="F4" s="30" t="n"/>
+      <c r="G4" s="30">
         <f>IF(C4="","",(COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,C4)+1)/2)/COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2484,31 +2498,31 @@
         <f>IF(G4="","",IF(G4&lt;=20%,"Q1 Cheapest",IF(G4&lt;=40%,"Q2",IF(G4&lt;=60%,"Q3",IF(G4&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="30">
         <f>IFERROR(B8/B4-1,"")</f>
         <v/>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="30">
         <f>IFERROR((B16/B4)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="30">
         <f>IFERROR((B24/B4)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L4" s="16">
+      <c r="L4" s="30">
         <f>IFERROR((B44/B4)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>42643</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>9463.610000000001</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>25.07</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2516,12 +2530,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="33">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
-      <c r="F5" s="16" t="n"/>
-      <c r="G5" s="16">
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="30">
         <f>IF(C5="","",(COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,C5)+1)/2)/COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2529,28 +2543,28 @@
         <f>IF(G5="","",IF(G5&lt;=20%,"Q1 Cheapest",IF(G5&lt;=40%,"Q2",IF(G5&lt;=60%,"Q3",IF(G5&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="30">
         <f>IFERROR(B9/B5-1,"")</f>
         <v/>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="30">
         <f>IFERROR((B17/B5)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="30">
         <f>IFERROR((B25/B5)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L5" s="16" t="n"/>
+      <c r="L5" s="30" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>42735</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>8536.01</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>20.46</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2558,15 +2572,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="33">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="30">
         <f>IF(AND(D6=D2,E2&lt;&gt;""),E6/E2-1,"")</f>
         <v/>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="30">
         <f>IF(C6="","",(COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,C6)+1)/2)/COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2574,28 +2588,28 @@
         <f>IF(G6="","",IF(G6&lt;=20%,"Q1 Cheapest",IF(G6&lt;=40%,"Q2",IF(G6&lt;=60%,"Q3",IF(G6&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="30">
         <f>IFERROR(B10/B6-1,"")</f>
         <v/>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="30">
         <f>IFERROR((B18/B6)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="30">
         <f>IFERROR((B26/B6)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L6" s="16" t="n"/>
+      <c r="L6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>42825</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>10803.04</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>21.64</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2603,15 +2617,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="33">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="30">
         <f>IF(AND(D7=D3,E3&lt;&gt;""),E7/E3-1,"")</f>
         <v/>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="30">
         <f>IF(C7="","",(COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,C7)+1)/2)/COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2619,28 +2633,28 @@
         <f>IF(G7="","",IF(G7&lt;=20%,"Q1 Cheapest",IF(G7&lt;=40%,"Q2",IF(G7&lt;=60%,"Q3",IF(G7&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="30">
         <f>IFERROR(B11/B7-1,"")</f>
         <v/>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="30">
         <f>IFERROR((B19/B7)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="30">
         <f>IFERROR((B27/B7)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L7" s="16" t="n"/>
+      <c r="L7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>42916</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>11462.19</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>20.77</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2648,15 +2662,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="33">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="30">
         <f>IF(AND(D8=D4,E4&lt;&gt;""),E8/E4-1,"")</f>
         <v/>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="30">
         <f>IF(C8="","",(COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,C8)+1)/2)/COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2664,28 +2678,28 @@
         <f>IF(G8="","",IF(G8&lt;=20%,"Q1 Cheapest",IF(G8&lt;=40%,"Q2",IF(G8&lt;=60%,"Q3",IF(G8&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="30">
         <f>IFERROR(B12/B8-1,"")</f>
         <v/>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="30">
         <f>IFERROR((B20/B8)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="30">
         <f>IFERROR((B28/B8)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L8" s="16" t="n"/>
+      <c r="L8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>43008</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>12229.89</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>57.65</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2693,15 +2707,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="33">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="30">
         <f>IF(AND(D9=D5,E5&lt;&gt;""),E9/E5-1,"")</f>
         <v/>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="30">
         <f>IF(C9="","",(COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,C9)+1)/2)/COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2709,28 +2723,28 @@
         <f>IF(G9="","",IF(G9&lt;=20%,"Q1 Cheapest",IF(G9&lt;=40%,"Q2",IF(G9&lt;=60%,"Q3",IF(G9&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="30">
         <f>IFERROR(B13/B9-1,"")</f>
         <v/>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="30">
         <f>IFERROR((B21/B9)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="30">
         <f>IFERROR((B29/B9)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L9" s="16" t="n"/>
+      <c r="L9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>43100</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>14257.54</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>89.66</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2738,15 +2752,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="33">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="30">
         <f>IF(AND(D10=D6,E6&lt;&gt;""),E10/E6-1,"")</f>
         <v/>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="30">
         <f>IF(C10="","",(COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,C10)+1)/2)/COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2754,28 +2768,28 @@
         <f>IF(G10="","",IF(G10&lt;=20%,"Q1 Cheapest",IF(G10&lt;=40%,"Q2",IF(G10&lt;=60%,"Q3",IF(G10&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="30">
         <f>IFERROR(B14/B10-1,"")</f>
         <v/>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="30">
         <f>IFERROR((B22/B10)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="30">
         <f>IFERROR((B30/B10)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L10" s="16" t="n"/>
+      <c r="L10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>43190</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>12558.6</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>57.68</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2783,15 +2797,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="33">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="30">
         <f>IF(AND(D11=D7,E7&lt;&gt;""),E11/E7-1,"")</f>
         <v/>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="30">
         <f>IF(C11="","",(COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,C11)+1)/2)/COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2799,28 +2813,28 @@
         <f>IF(G11="","",IF(G11&lt;=20%,"Q1 Cheapest",IF(G11&lt;=40%,"Q2",IF(G11&lt;=60%,"Q3",IF(G11&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="30">
         <f>IFERROR(B15/B11-1,"")</f>
         <v/>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="30">
         <f>IFERROR((B23/B11)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="30">
         <f>IFERROR((B31/B11)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L11" s="16" t="n"/>
+      <c r="L11" s="30" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>43281</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>12897.05</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>30.28</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2828,15 +2842,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="33">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="30">
         <f>IF(AND(D12=D8,E8&lt;&gt;""),E12/E8-1,"")</f>
         <v/>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="30">
         <f>IF(C12="","",(COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,C12)+1)/2)/COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2844,28 +2858,28 @@
         <f>IF(G12="","",IF(G12&lt;=20%,"Q1 Cheapest",IF(G12&lt;=40%,"Q2",IF(G12&lt;=60%,"Q3",IF(G12&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="30">
         <f>IFERROR(B16/B12-1,"")</f>
         <v/>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="30">
         <f>IFERROR((B24/B12)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="30">
         <f>IFERROR((B32/B12)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L12" s="16" t="n"/>
+      <c r="L12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>43373</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>12415.75</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>25.26</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2873,15 +2887,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="33">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="30">
         <f>IF(AND(D13=D9,E9&lt;&gt;""),E13/E9-1,"")</f>
         <v/>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="30">
         <f>IF(C13="","",(COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,C13)+1)/2)/COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2889,28 +2903,28 @@
         <f>IF(G13="","",IF(G13&lt;=20%,"Q1 Cheapest",IF(G13&lt;=40%,"Q2",IF(G13&lt;=60%,"Q3",IF(G13&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="30">
         <f>IFERROR(B17/B13-1,"")</f>
         <v/>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="30">
         <f>IFERROR((B25/B13)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="30">
         <f>IFERROR((B33/B13)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L13" s="16" t="n"/>
+      <c r="L13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>43465</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>12191.25</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>26.01</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2918,15 +2932,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="33">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="30">
         <f>IF(AND(D14=D10,E10&lt;&gt;""),E14/E10-1,"")</f>
         <v/>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="30">
         <f>IF(C14="","",(COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,C14)+1)/2)/COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2934,28 +2948,28 @@
         <f>IF(G14="","",IF(G14&lt;=20%,"Q1 Cheapest",IF(G14&lt;=40%,"Q2",IF(G14&lt;=60%,"Q3",IF(G14&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="30">
         <f>IFERROR(B18/B14-1,"")</f>
         <v/>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="30">
         <f>IFERROR((B26/B14)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="30">
         <f>IFERROR((B34/B14)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L14" s="16" t="n"/>
+      <c r="L14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>43555</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>12187.9</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>44.7</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2963,15 +2977,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="33">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="30">
         <f>IF(AND(D15=D11,E11&lt;&gt;""),E15/E11-1,"")</f>
         <v/>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="30">
         <f>IF(C15="","",(COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,C15)+1)/2)/COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2979,28 +2993,28 @@
         <f>IF(G15="","",IF(G15&lt;=20%,"Q1 Cheapest",IF(G15&lt;=40%,"Q2",IF(G15&lt;=60%,"Q3",IF(G15&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="30">
         <f>IFERROR(B19/B15-1,"")</f>
         <v/>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="30">
         <f>IFERROR((B27/B15)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="30">
         <f>IFERROR((B35/B15)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L15" s="16" t="n"/>
+      <c r="L15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>43646</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>12373.9</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>42.25</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3008,15 +3022,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="33">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="30">
         <f>IF(AND(D16=D12,E12&lt;&gt;""),E16/E12-1,"")</f>
         <v/>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="30">
         <f>IF(C16="","",(COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,C16)+1)/2)/COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3024,28 +3038,28 @@
         <f>IF(G16="","",IF(G16&lt;=20%,"Q1 Cheapest",IF(G16&lt;=40%,"Q2",IF(G16&lt;=60%,"Q3",IF(G16&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="30">
         <f>IFERROR(B20/B16-1,"")</f>
         <v/>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="30">
         <f>IFERROR((B28/B16)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="30">
         <f>IFERROR((B36/B16)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L16" s="16" t="n"/>
+      <c r="L16" s="30" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>43738</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>12401.8</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>29.72</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3053,15 +3067,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="33">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="30">
         <f>IF(AND(D17=D13,E13&lt;&gt;""),E17/E13-1,"")</f>
         <v/>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="30">
         <f>IF(C17="","",(COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,C17)+1)/2)/COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3069,28 +3083,28 @@
         <f>IF(G17="","",IF(G17&lt;=20%,"Q1 Cheapest",IF(G17&lt;=40%,"Q2",IF(G17&lt;=60%,"Q3",IF(G17&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="30">
         <f>IFERROR(B21/B17-1,"")</f>
         <v/>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="30">
         <f>IFERROR((B29/B17)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K17" s="16">
+      <c r="K17" s="30">
         <f>IFERROR((B37/B17)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L17" s="16" t="n"/>
+      <c r="L17" s="30" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>43830</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>13071.95</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>35.82</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3098,15 +3112,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="33">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="30">
         <f>IF(AND(D18=D14,E14&lt;&gt;""),E18/E14-1,"")</f>
         <v/>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="30">
         <f>IF(C18="","",(COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,C18)+1)/2)/COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3114,28 +3128,28 @@
         <f>IF(G18="","",IF(G18&lt;=20%,"Q1 Cheapest",IF(G18&lt;=40%,"Q2",IF(G18&lt;=60%,"Q3",IF(G18&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="30">
         <f>IFERROR(B22/B18-1,"")</f>
         <v/>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="30">
         <f>IFERROR((B30/B18)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="30">
         <f>IFERROR((B38/B18)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L18" s="16" t="n"/>
+      <c r="L18" s="30" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>43921</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>10067.55</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>25.47</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -3143,15 +3157,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="33">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="30">
         <f>IF(AND(D19=D15,E15&lt;&gt;""),E19/E15-1,"")</f>
         <v/>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="30">
         <f>IF(C19="","",(COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,C19)+1)/2)/COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3159,28 +3173,28 @@
         <f>IF(G19="","",IF(G19&lt;=20%,"Q1 Cheapest",IF(G19&lt;=40%,"Q2",IF(G19&lt;=60%,"Q3",IF(G19&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="30">
         <f>IFERROR(B23/B19-1,"")</f>
         <v/>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="30">
         <f>IFERROR((B31/B19)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K19" s="16">
+      <c r="K19" s="30">
         <f>IFERROR((B39/B19)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L19" s="16" t="n"/>
+      <c r="L19" s="30" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44012</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>13701.05</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>37.56</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -3188,15 +3202,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="33">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="30">
         <f>IF(AND(D20=D16,E16&lt;&gt;""),E20/E16-1,"")</f>
         <v/>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="30">
         <f>IF(C20="","",(COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,C20)+1)/2)/COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3204,42 +3218,42 @@
         <f>IF(G20="","",IF(G20&lt;=20%,"Q1 Cheapest",IF(G20&lt;=40%,"Q2",IF(G20&lt;=60%,"Q3",IF(G20&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="30">
         <f>IFERROR(B24/B20-1,"")</f>
         <v/>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="30">
         <f>IFERROR((B32/B20)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="30">
         <f>IFERROR((B40/B20)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L20" s="16" t="n"/>
+      <c r="L20" s="30" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44104</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>16926.65</v>
       </c>
-      <c r="C21" s="7" t="n"/>
+      <c r="C21" s="25" t="n"/>
       <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="33">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="30">
         <f>IF(AND(D21=D17,E17&lt;&gt;""),E21/E17-1,"")</f>
         <v/>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="30">
         <f>IF(C21="","",(COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,C21)+1)/2)/COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3247,42 +3261,42 @@
         <f>IF(G21="","",IF(G21&lt;=20%,"Q1 Cheapest",IF(G21&lt;=40%,"Q2",IF(G21&lt;=60%,"Q3",IF(G21&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="30">
         <f>IFERROR(B25/B21-1,"")</f>
         <v/>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="30">
         <f>IFERROR((B33/B21)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="30">
         <f>IFERROR((B41/B21)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L21" s="16" t="n"/>
+      <c r="L21" s="30" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44196</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>19836.8</v>
       </c>
-      <c r="C22" s="7" t="n"/>
+      <c r="C22" s="25" t="n"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="33">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="30">
         <f>IF(AND(D22=D18,E18&lt;&gt;""),E22/E18-1,"")</f>
         <v/>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="30">
         <f>IF(C22="","",(COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,C22)+1)/2)/COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3290,42 +3304,42 @@
         <f>IF(G22="","",IF(G22&lt;=20%,"Q1 Cheapest",IF(G22&lt;=40%,"Q2",IF(G22&lt;=60%,"Q3",IF(G22&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="30">
         <f>IFERROR(B26/B22-1,"")</f>
         <v/>
       </c>
-      <c r="J22" s="16">
+      <c r="J22" s="30">
         <f>IFERROR((B34/B22)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K22" s="16">
+      <c r="K22" s="30">
         <f>IFERROR((B42/B22)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L22" s="16" t="n"/>
+      <c r="L22" s="30" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>44286</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>22648.2</v>
       </c>
-      <c r="C23" s="7" t="n"/>
+      <c r="C23" s="25" t="n"/>
       <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="33">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="30">
         <f>IF(AND(D23=D19,E19&lt;&gt;""),E23/E19-1,"")</f>
         <v/>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="30">
         <f>IF(C23="","",(COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,C23)+1)/2)/COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3333,28 +3347,28 @@
         <f>IF(G23="","",IF(G23&lt;=20%,"Q1 Cheapest",IF(G23&lt;=40%,"Q2",IF(G23&lt;=60%,"Q3",IF(G23&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="30">
         <f>IFERROR(B27/B23-1,"")</f>
         <v/>
       </c>
-      <c r="J23" s="16">
+      <c r="J23" s="30">
         <f>IFERROR((B35/B23)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K23" s="16">
+      <c r="K23" s="30">
         <f>IFERROR((B43/B23)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L23" s="16" t="n"/>
+      <c r="L23" s="30" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>27135</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>55.12</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3362,15 +3376,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="33">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="30">
         <f>IF(AND(D24=D20,E20&lt;&gt;""),E24/E20-1,"")</f>
         <v/>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="30">
         <f>IF(C24="","",(COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,C24)+1)/2)/COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3378,28 +3392,28 @@
         <f>IF(G24="","",IF(G24&lt;=20%,"Q1 Cheapest",IF(G24&lt;=40%,"Q2",IF(G24&lt;=60%,"Q3",IF(G24&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="30">
         <f>IFERROR(B28/B24-1,"")</f>
         <v/>
       </c>
-      <c r="J24" s="16">
+      <c r="J24" s="30">
         <f>IFERROR((B36/B24)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K24" s="16">
+      <c r="K24" s="30">
         <f>IFERROR((B44/B24)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L24" s="16" t="n"/>
+      <c r="L24" s="30" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>31641.8</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>36.37</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3407,15 +3421,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="33">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="30">
         <f>IF(AND(D25=D21,E21&lt;&gt;""),E25/E21-1,"")</f>
         <v/>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="30">
         <f>IF(C25="","",(COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,C25)+1)/2)/COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3423,25 +3437,25 @@
         <f>IF(G25="","",IF(G25&lt;=20%,"Q1 Cheapest",IF(G25&lt;=40%,"Q2",IF(G25&lt;=60%,"Q3",IF(G25&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="30">
         <f>IFERROR(B29/B25-1,"")</f>
         <v/>
       </c>
-      <c r="J25" s="16">
+      <c r="J25" s="30">
         <f>IFERROR((B37/B25)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K25" s="16" t="n"/>
-      <c r="L25" s="16" t="n"/>
+      <c r="K25" s="30" t="n"/>
+      <c r="L25" s="30" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>34605.05</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>35.34</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3449,15 +3463,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="33">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="30">
         <f>IF(AND(D26=D22,E22&lt;&gt;""),E26/E22-1,"")</f>
         <v/>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="30">
         <f>IF(C26="","",(COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,C26)+1)/2)/COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3465,25 +3479,25 @@
         <f>IF(G26="","",IF(G26&lt;=20%,"Q1 Cheapest",IF(G26&lt;=40%,"Q2",IF(G26&lt;=60%,"Q3",IF(G26&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="30">
         <f>IFERROR(B30/B26-1,"")</f>
         <v/>
       </c>
-      <c r="J26" s="16">
+      <c r="J26" s="30">
         <f>IFERROR((B38/B26)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K26" s="16" t="n"/>
-      <c r="L26" s="16" t="n"/>
+      <c r="K26" s="30" t="n"/>
+      <c r="L26" s="30" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>35463.05</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>31.75</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3491,15 +3505,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E27" s="21">
+      <c r="E27" s="33">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="30">
         <f>IF(AND(D27=D23,E23&lt;&gt;""),E27/E23-1,"")</f>
         <v/>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="30">
         <f>IF(C27="","",(COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,C27)+1)/2)/COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3507,25 +3521,25 @@
         <f>IF(G27="","",IF(G27&lt;=20%,"Q1 Cheapest",IF(G27&lt;=40%,"Q2",IF(G27&lt;=60%,"Q3",IF(G27&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="30">
         <f>IFERROR(B31/B27-1,"")</f>
         <v/>
       </c>
-      <c r="J27" s="16">
+      <c r="J27" s="30">
         <f>IFERROR((B39/B27)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K27" s="16" t="n"/>
-      <c r="L27" s="16" t="n"/>
+      <c r="K27" s="30" t="n"/>
+      <c r="L27" s="30" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>26214.1</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>29.75</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3533,15 +3547,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E28" s="21">
+      <c r="E28" s="33">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="30">
         <f>IF(AND(D28=D24,E24&lt;&gt;""),E28/E24-1,"")</f>
         <v/>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="30">
         <f>IF(C28="","",(COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,C28)+1)/2)/COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3549,25 +3563,25 @@
         <f>IF(G28="","",IF(G28&lt;=20%,"Q1 Cheapest",IF(G28&lt;=40%,"Q2",IF(G28&lt;=60%,"Q3",IF(G28&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="30">
         <f>IFERROR(B32/B28-1,"")</f>
         <v/>
       </c>
-      <c r="J28" s="16">
+      <c r="J28" s="30">
         <f>IFERROR((B40/B28)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K28" s="16" t="n"/>
-      <c r="L28" s="16" t="n"/>
+      <c r="K28" s="30" t="n"/>
+      <c r="L28" s="30" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>29586.2</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>41.96</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3575,15 +3589,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E29" s="21">
+      <c r="E29" s="33">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="30">
         <f>IF(AND(D29=D25,E25&lt;&gt;""),E29/E25-1,"")</f>
         <v/>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="30">
         <f>IF(C29="","",(COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,C29)+1)/2)/COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3591,25 +3605,25 @@
         <f>IF(G29="","",IF(G29&lt;=20%,"Q1 Cheapest",IF(G29&lt;=40%,"Q2",IF(G29&lt;=60%,"Q3",IF(G29&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="30">
         <f>IFERROR(B33/B29-1,"")</f>
         <v/>
       </c>
-      <c r="J29" s="16">
+      <c r="J29" s="30">
         <f>IFERROR((B41/B29)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K29" s="16" t="n"/>
-      <c r="L29" s="16" t="n"/>
+      <c r="K29" s="30" t="n"/>
+      <c r="L29" s="30" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>29685.5</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>17.97</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3617,15 +3631,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="33">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="30">
         <f>IF(AND(D30=D26,E26&lt;&gt;""),E30/E26-1,"")</f>
         <v/>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="30">
         <f>IF(C30="","",(COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,C30)+1)/2)/COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3633,25 +3647,25 @@
         <f>IF(G30="","",IF(G30&lt;=20%,"Q1 Cheapest",IF(G30&lt;=40%,"Q2",IF(G30&lt;=60%,"Q3",IF(G30&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="30">
         <f>IFERROR(B34/B30-1,"")</f>
         <v/>
       </c>
-      <c r="J30" s="16">
+      <c r="J30" s="30">
         <f>IFERROR((B42/B30)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K30" s="16" t="n"/>
-      <c r="L30" s="16" t="n"/>
+      <c r="K30" s="30" t="n"/>
+      <c r="L30" s="30" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>25993.55</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>15.12</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -3659,15 +3673,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E31" s="21">
+      <c r="E31" s="33">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="30">
         <f>IF(AND(D31=D27,E27&lt;&gt;""),E31/E27-1,"")</f>
         <v/>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="30">
         <f>IF(C31="","",(COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,C31)+1)/2)/COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3675,25 +3689,25 @@
         <f>IF(G31="","",IF(G31&lt;=20%,"Q1 Cheapest",IF(G31&lt;=40%,"Q2",IF(G31&lt;=60%,"Q3",IF(G31&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="30">
         <f>IFERROR(B35/B31-1,"")</f>
         <v/>
       </c>
-      <c r="J31" s="16">
+      <c r="J31" s="30">
         <f>IFERROR((B43/B31)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K31" s="16" t="n"/>
-      <c r="L31" s="16" t="n"/>
+      <c r="K31" s="30" t="n"/>
+      <c r="L31" s="30" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>31290.15</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>16.42</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3701,15 +3715,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E32" s="21">
+      <c r="E32" s="33">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="30">
         <f>IF(AND(D32=D28,E28&lt;&gt;""),E32/E28-1,"")</f>
         <v/>
       </c>
-      <c r="G32" s="16">
+      <c r="G32" s="30">
         <f>IF(C32="","",(COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,C32)+1)/2)/COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3717,25 +3731,25 @@
         <f>IF(G32="","",IF(G32&lt;=20%,"Q1 Cheapest",IF(G32&lt;=40%,"Q2",IF(G32&lt;=60%,"Q3",IF(G32&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="30">
         <f>IFERROR(B36/B32-1,"")</f>
         <v/>
       </c>
-      <c r="J32" s="16">
+      <c r="J32" s="30">
         <f>IFERROR((B44/B32)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K32" s="16" t="n"/>
-      <c r="L32" s="16" t="n"/>
+      <c r="K32" s="30" t="n"/>
+      <c r="L32" s="30" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>36496.65</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>16.04</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -3743,15 +3757,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E33" s="21">
+      <c r="E33" s="33">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="30">
         <f>IF(AND(D33=D29,E29&lt;&gt;""),E33/E29-1,"")</f>
         <v/>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="30">
         <f>IF(C33="","",(COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,C33)+1)/2)/COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3759,22 +3773,22 @@
         <f>IF(G33="","",IF(G33&lt;=20%,"Q1 Cheapest",IF(G33&lt;=40%,"Q2",IF(G33&lt;=60%,"Q3",IF(G33&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I33" s="16">
+      <c r="I33" s="30">
         <f>IFERROR(B37/B33-1,"")</f>
         <v/>
       </c>
-      <c r="J33" s="16" t="n"/>
-      <c r="K33" s="16" t="n"/>
-      <c r="L33" s="16" t="n"/>
+      <c r="J33" s="30" t="n"/>
+      <c r="K33" s="30" t="n"/>
+      <c r="L33" s="30" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>42306.3</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>26.68</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3782,15 +3796,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E34" s="21">
+      <c r="E34" s="33">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="30">
         <f>IF(AND(D34=D30,E30&lt;&gt;""),E34/E30-1,"")</f>
         <v/>
       </c>
-      <c r="G34" s="16">
+      <c r="G34" s="30">
         <f>IF(C34="","",(COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,C34)+1)/2)/COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3798,22 +3812,22 @@
         <f>IF(G34="","",IF(G34&lt;=20%,"Q1 Cheapest",IF(G34&lt;=40%,"Q2",IF(G34&lt;=60%,"Q3",IF(G34&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I34" s="16">
+      <c r="I34" s="30">
         <f>IFERROR(B38/B34-1,"")</f>
         <v/>
       </c>
-      <c r="J34" s="16" t="n"/>
-      <c r="K34" s="16" t="n"/>
-      <c r="L34" s="16" t="n"/>
+      <c r="J34" s="30" t="n"/>
+      <c r="K34" s="30" t="n"/>
+      <c r="L34" s="30" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>47200.3</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>27.39</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -3821,15 +3835,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E35" s="21">
+      <c r="E35" s="33">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="30">
         <f>IF(AND(D35=D31,E31&lt;&gt;""),E35/E31-1,"")</f>
         <v/>
       </c>
-      <c r="G35" s="16">
+      <c r="G35" s="30">
         <f>IF(C35="","",(COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,C35)+1)/2)/COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3837,22 +3851,22 @@
         <f>IF(G35="","",IF(G35&lt;=20%,"Q1 Cheapest",IF(G35&lt;=40%,"Q2",IF(G35&lt;=60%,"Q3",IF(G35&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I35" s="16">
+      <c r="I35" s="30">
         <f>IFERROR(B39/B35-1,"")</f>
         <v/>
       </c>
-      <c r="J35" s="16" t="n"/>
-      <c r="K35" s="16" t="n"/>
-      <c r="L35" s="16" t="n"/>
+      <c r="J35" s="30" t="n"/>
+      <c r="K35" s="30" t="n"/>
+      <c r="L35" s="30" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>56314.8</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>30.79</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3860,15 +3874,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E36" s="21">
+      <c r="E36" s="33">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="30">
         <f>IF(AND(D36=D32,E32&lt;&gt;""),E36/E32-1,"")</f>
         <v/>
       </c>
-      <c r="G36" s="16">
+      <c r="G36" s="30">
         <f>IF(C36="","",(COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,C36)+1)/2)/COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3876,22 +3890,22 @@
         <f>IF(G36="","",IF(G36&lt;=20%,"Q1 Cheapest",IF(G36&lt;=40%,"Q2",IF(G36&lt;=60%,"Q3",IF(G36&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I36" s="16">
+      <c r="I36" s="30">
         <f>IFERROR(B40/B36-1,"")</f>
         <v/>
       </c>
-      <c r="J36" s="16" t="n"/>
-      <c r="K36" s="16" t="n"/>
-      <c r="L36" s="16" t="n"/>
+      <c r="J36" s="30" t="n"/>
+      <c r="K36" s="30" t="n"/>
+      <c r="L36" s="30" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="24" t="n">
         <v>60409.8</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="25" t="n">
         <v>41.61</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -3899,15 +3913,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E37" s="21">
+      <c r="E37" s="33">
         <f>IFERROR(B37/C37,"")</f>
         <v/>
       </c>
-      <c r="F37" s="16">
+      <c r="F37" s="30">
         <f>IF(AND(D37=D33,E33&lt;&gt;""),E37/E33-1,"")</f>
         <v/>
       </c>
-      <c r="G37" s="16">
+      <c r="G37" s="30">
         <f>IF(C37="","",(COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,C37)+1)/2)/COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3915,22 +3929,22 @@
         <f>IF(G37="","",IF(G37&lt;=20%,"Q1 Cheapest",IF(G37&lt;=40%,"Q2",IF(G37&lt;=60%,"Q3",IF(G37&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I37" s="16">
+      <c r="I37" s="30">
         <f>IFERROR(B41/B37-1,"")</f>
         <v/>
       </c>
-      <c r="J37" s="16" t="n"/>
-      <c r="K37" s="16" t="n"/>
-      <c r="L37" s="16" t="n"/>
+      <c r="J37" s="30" t="n"/>
+      <c r="K37" s="30" t="n"/>
+      <c r="L37" s="30" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="24" t="n">
         <v>56293.05</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="25" t="n">
         <v>42.38</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3938,15 +3952,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E38" s="21">
+      <c r="E38" s="33">
         <f>IFERROR(B38/C38,"")</f>
         <v/>
       </c>
-      <c r="F38" s="16">
+      <c r="F38" s="30">
         <f>IF(AND(D38=D34,E34&lt;&gt;""),E38/E34-1,"")</f>
         <v/>
       </c>
-      <c r="G38" s="16">
+      <c r="G38" s="30">
         <f>IF(C38="","",(COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,C38)+1)/2)/COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3954,22 +3968,22 @@
         <f>IF(G38="","",IF(G38&lt;=20%,"Q1 Cheapest",IF(G38&lt;=40%,"Q2",IF(G38&lt;=60%,"Q3",IF(G38&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I38" s="16">
+      <c r="I38" s="30">
         <f>IFERROR(B42/B38-1,"")</f>
         <v/>
       </c>
-      <c r="J38" s="16" t="n"/>
-      <c r="K38" s="16" t="n"/>
-      <c r="L38" s="16" t="n"/>
+      <c r="J38" s="30" t="n"/>
+      <c r="K38" s="30" t="n"/>
+      <c r="L38" s="30" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="24" t="n">
         <v>46004.55</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="25" t="n">
         <v>41.36</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -3977,15 +3991,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E39" s="21">
+      <c r="E39" s="33">
         <f>IFERROR(B39/C39,"")</f>
         <v/>
       </c>
-      <c r="F39" s="16">
+      <c r="F39" s="30">
         <f>IF(AND(D39=D35,E35&lt;&gt;""),E39/E35-1,"")</f>
         <v/>
       </c>
-      <c r="G39" s="16">
+      <c r="G39" s="30">
         <f>IF(C39="","",(COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,C39)+1)/2)/COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3993,22 +4007,22 @@
         <f>IF(G39="","",IF(G39&lt;=20%,"Q1 Cheapest",IF(G39&lt;=40%,"Q2",IF(G39&lt;=60%,"Q3",IF(G39&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I39" s="16">
+      <c r="I39" s="30">
         <f>IFERROR(B43/B39-1,"")</f>
         <v/>
       </c>
-      <c r="J39" s="16" t="n"/>
-      <c r="K39" s="16" t="n"/>
-      <c r="L39" s="16" t="n"/>
+      <c r="J39" s="30" t="n"/>
+      <c r="K39" s="30" t="n"/>
+      <c r="L39" s="30" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="24" t="n">
         <v>53900.45</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="25" t="n">
         <v>51.51</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -4016,15 +4030,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E40" s="21">
+      <c r="E40" s="33">
         <f>IFERROR(B40/C40,"")</f>
         <v/>
       </c>
-      <c r="F40" s="16">
+      <c r="F40" s="30">
         <f>IF(AND(D40=D36,E36&lt;&gt;""),E40/E36-1,"")</f>
         <v/>
       </c>
-      <c r="G40" s="16">
+      <c r="G40" s="30">
         <f>IF(C40="","",(COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,C40)+1)/2)/COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4032,22 +4046,22 @@
         <f>IF(G40="","",IF(G40&lt;=20%,"Q1 Cheapest",IF(G40&lt;=40%,"Q2",IF(G40&lt;=60%,"Q3",IF(G40&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I40" s="16">
+      <c r="I40" s="30">
         <f>IFERROR(B44/B40-1,"")</f>
         <v/>
       </c>
-      <c r="J40" s="16" t="n"/>
-      <c r="K40" s="16" t="n"/>
-      <c r="L40" s="16" t="n"/>
+      <c r="J40" s="30" t="n"/>
+      <c r="K40" s="30" t="n"/>
+      <c r="L40" s="30" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="24" t="n">
         <v>48722.95</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="25" t="n">
         <v>40.37</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -4055,15 +4069,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E41" s="21">
+      <c r="E41" s="33">
         <f>IFERROR(B41/C41,"")</f>
         <v/>
       </c>
-      <c r="F41" s="16">
+      <c r="F41" s="30">
         <f>IF(AND(D41=D37,E37&lt;&gt;""),E41/E37-1,"")</f>
         <v/>
       </c>
-      <c r="G41" s="16">
+      <c r="G41" s="30">
         <f>IF(C41="","",(COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,C41)+1)/2)/COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4071,19 +4085,19 @@
         <f>IF(G41="","",IF(G41&lt;=20%,"Q1 Cheapest",IF(G41&lt;=40%,"Q2",IF(G41&lt;=60%,"Q3",IF(G41&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I41" s="16" t="n"/>
-      <c r="J41" s="16" t="n"/>
-      <c r="K41" s="16" t="n"/>
-      <c r="L41" s="16" t="n"/>
+      <c r="I41" s="30" t="n"/>
+      <c r="J41" s="30" t="n"/>
+      <c r="K41" s="30" t="n"/>
+      <c r="L41" s="30" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="24" t="n">
         <v>50309.15</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="25" t="n">
         <v>33.05</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -4091,15 +4105,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E42" s="21">
+      <c r="E42" s="33">
         <f>IFERROR(B42/C42,"")</f>
         <v/>
       </c>
-      <c r="F42" s="16">
+      <c r="F42" s="30">
         <f>IF(AND(D42=D38,E38&lt;&gt;""),E42/E38-1,"")</f>
         <v/>
       </c>
-      <c r="G42" s="16">
+      <c r="G42" s="30">
         <f>IF(C42="","",(COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,C42)+1)/2)/COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4107,19 +4121,19 @@
         <f>IF(G42="","",IF(G42&lt;=20%,"Q1 Cheapest",IF(G42&lt;=40%,"Q2",IF(G42&lt;=60%,"Q3",IF(G42&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I42" s="16" t="n"/>
-      <c r="J42" s="16" t="n"/>
-      <c r="K42" s="16" t="n"/>
-      <c r="L42" s="16" t="n"/>
+      <c r="I42" s="30" t="n"/>
+      <c r="J42" s="30" t="n"/>
+      <c r="K42" s="30" t="n"/>
+      <c r="L42" s="30" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n">
+      <c r="A43" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="24" t="n">
         <v>44487.95</v>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="25" t="n">
         <v>23.91</v>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -4127,15 +4141,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E43" s="21">
+      <c r="E43" s="33">
         <f>IFERROR(B43/C43,"")</f>
         <v/>
       </c>
-      <c r="F43" s="16">
+      <c r="F43" s="30">
         <f>IF(AND(D43=D39,E39&lt;&gt;""),E43/E39-1,"")</f>
         <v/>
       </c>
-      <c r="G43" s="16">
+      <c r="G43" s="30">
         <f>IF(C43="","",(COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C43)+(COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,C43)+1)/2)/COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4143,19 +4157,19 @@
         <f>IF(G43="","",IF(G43&lt;=20%,"Q1 Cheapest",IF(G43&lt;=40%,"Q2",IF(G43&lt;=60%,"Q3",IF(G43&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I43" s="16" t="n"/>
-      <c r="J43" s="16" t="n"/>
-      <c r="K43" s="16" t="n"/>
-      <c r="L43" s="16" t="n"/>
+      <c r="I43" s="30" t="n"/>
+      <c r="J43" s="30" t="n"/>
+      <c r="K43" s="30" t="n"/>
+      <c r="L43" s="30" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="n">
+      <c r="A44" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" s="24" t="n">
         <v>53700.3</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="25" t="n">
         <v>24.79</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -4163,15 +4177,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E44" s="21">
+      <c r="E44" s="33">
         <f>IFERROR(B44/C44,"")</f>
         <v/>
       </c>
-      <c r="F44" s="16">
+      <c r="F44" s="30">
         <f>IF(AND(D44=D40,E40&lt;&gt;""),E44/E40-1,"")</f>
         <v/>
       </c>
-      <c r="G44" s="16">
+      <c r="G44" s="30">
         <f>IF(C44="","",(COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C44)+(COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,C44)+1)/2)/COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4179,10 +4193,10 @@
         <f>IF(G44="","",IF(G44&lt;=20%,"Q1 Cheapest",IF(G44&lt;=40%,"Q2",IF(G44&lt;=60%,"Q3",IF(G44&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I44" s="16" t="n"/>
-      <c r="J44" s="16" t="n"/>
-      <c r="K44" s="16" t="n"/>
-      <c r="L44" s="16" t="n"/>
+      <c r="I44" s="30" t="n"/>
+      <c r="J44" s="30" t="n"/>
+      <c r="K44" s="30" t="n"/>
+      <c r="L44" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -4259,30 +4273,30 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>46283</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>56192.35</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>23.48</v>
       </c>
-      <c r="D2" s="8" t="n">
+      <c r="D2" s="26" t="n">
         <v>0.1953125</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="26" t="n">
         <v>1.05957240785</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="34">
         <f>IF(D2="","",100*(1-D2))</f>
         <v/>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="34">
         <f>IF(E2="","",IF(E2&lt;=0,20,IF(E2&lt;5%,20+400*E2,IF(E2&lt;10%,40+400*(E2-5%),IF(E2&lt;15%,60+400*(E2-10%),IF(E2&lt;25%,80+200*(E2-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="34">
         <f>IF(OR(F2="",G2=""),"",70%*F2+30%*G2)</f>
         <v/>
       </c>
@@ -4292,30 +4306,30 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>46286</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>55808.95</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>23.32</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="26" t="n">
         <v>0.1953125</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="26" t="n">
         <v>1.0596215628</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="34">
         <f>IF(D3="","",100*(1-D3))</f>
         <v/>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="34">
         <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="34">
         <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
         <v/>
       </c>
@@ -4325,30 +4339,30 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>46287</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>55466.15</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>23.18</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="26" t="n">
         <v>0.1953125</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="26" t="n">
         <v>1.05932423572</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="34">
         <f>IF(D4="","",100*(1-D4))</f>
         <v/>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="34">
         <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="34">
         <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
         <v/>
       </c>
@@ -4468,4 +4482,43 @@
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>Nifty Alpha 50 Composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Official composition data is not currently available for this index.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/downloads/indices/nifty-alpha-50.xlsx
+++ b/docs/downloads/indices/nifty-alpha-50.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Monthly PE History" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Quarterly Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Score History" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Composition" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Composition" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sources &amp; Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -110,7 +110,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -153,6 +153,9 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4381,6 +4384,1112 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>NIFTY Alpha 50 Composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>As of</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Retrieved 2026-09-23</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Weight coverage</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>NSE Indices — Index Constituent CSV</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Top 10 weight</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>Sector / Industry</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Acutaas Chemicals Ltd.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ACUTAAS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Adani Energy Solutions Ltd.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ADANIENSOL</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Adani Power Ltd.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Aditya Birla Capital Ltd.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ABCAPITAL</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Amber Enterprises India Ltd.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Anand Rathi Wealth Ltd.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ANANDRATHI</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Apar Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>APARINDS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ashok Leyland Ltd.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ather Energy Ltd.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ATHERENERG</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>AU Small Finance Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Bank of India</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BANKINDIA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Bharat Forge Ltd.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Bharat Heavy Electricals Ltd.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BSE Ltd.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BSE</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Canara Bank</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CANBK</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cummins India Ltd.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CUMMINSIND</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Delhivery Ltd.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DELHIVERY</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Eicher Motors Ltd.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Federal Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Fortis Healthcare Ltd.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>FORTIS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FSN E-Commerce Ventures Ltd.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>GE Vernova T&amp;D India Ltd.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>GVT&amp;D</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Glenmark Pharmaceuticals Ltd.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>HDFC Asset Management Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>HDFCAMC</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Hindalco Industries Ltd.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Hindustan Copper Ltd.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Hitachi Energy India Ltd.</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>POWERINDIA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>IIFL Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>IIFL</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Indian Bank</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Karur Vysya Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>KARURVYSYA</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>L&amp;T Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>LTF</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>32</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Laurus Labs Ltd.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>33</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Manappuram Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>MANAPPURAM</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>34</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Max Financial Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>MFSL</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>35</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Multi Commodity Exchange of India Ltd.</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Muthoot Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>National Aluminium Co. Ltd.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Navin Fluorine International Ltd.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>NAVINFLUOR</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>One 97 Communications Ltd.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Polycab India Ltd.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Radico Khaitan Ltd</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>RADICO</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Fast Moving Consumer Goods</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>RBL Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Shriram Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Solar Industries India Ltd.</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SOLARINDS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>State Bank of India</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Steel Authority of India Ltd.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>TVS Motor Company Ltd.</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Automobile and Auto Components</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Union Bank of India</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Vedanta Ltd.</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>VEDL</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Metals &amp; Mining</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Vodafone Idea Ltd.</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>IDEA</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D11"/>
@@ -4482,43 +5591,4 @@
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="35" t="inlineStr">
-        <is>
-          <t>Nifty Alpha 50 Composition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Official composition data is not currently available for this index.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/downloads/indices/nifty-alpha-50.xlsx
+++ b/docs/downloads/indices/nifty-alpha-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>55466.15</v>
+        <v>55944.6</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23.18</v>
+        <v>23.38</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2392.845125107852</v>
+        <v>2392.84003421728</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>1.059324235722265</v>
+        <v>1.059347980405599</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04314063848144953</v>
+        <v>0.0427715996578272</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>29.75</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>71187.14247195858</v>
+        <v>71186.99101796407</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2834339948231233</v>
+        <v>0.2724550898203593</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>41.96</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>100403.7814495255</v>
+        <v>100403.5678357571</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.8101811906816221</v>
+        <v>0.7946963216424296</v>
       </c>
     </row>
     <row r="16">
@@ -4214,7 +4214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4371,6 +4371,39 @@
       </c>
       <c r="I4">
         <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B5" s="24" t="n">
+        <v>55944.6</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="D5" s="26" t="n">
+        <v>0.1953125</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>1.05934798041</v>
+      </c>
+      <c r="F5" s="34">
+        <f>IF(D5="","",100*(1-D5))</f>
+        <v/>
+      </c>
+      <c r="G5" s="34">
+        <f>IF(E5="","",IF(E5&lt;=0,20,IF(E5&lt;5%,20+400*E5,IF(E5&lt;10%,40+400*(E5-5%),IF(E5&lt;15%,60+400*(E5-10%),IF(E5&lt;25%,80+200*(E5-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H5" s="34">
+        <f>IF(OR(F5="",G5=""),"",70%*F5+30%*G5)</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-alpha-50.xlsx
+++ b/docs/downloads/indices/nifty-alpha-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>55944.6</v>
+        <v>55067.35</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23.38</v>
+        <v>23.01</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2392.84003421728</v>
+        <v>2393.19209039548</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>1.059347980405599</v>
+        <v>1.059520142999616</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0427715996578272</v>
+        <v>0.0434593654932638</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>29.75</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>71186.99101796407</v>
+        <v>71197.46468926553</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2724550898203593</v>
+        <v>0.2929161234245978</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>41.96</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>100403.5678357571</v>
+        <v>100418.3401129944</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.7946963216424296</v>
+        <v>0.8235549760973491</v>
       </c>
     </row>
     <row r="16">
@@ -4214,7 +4214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4404,6 +4404,39 @@
       </c>
       <c r="I5">
         <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B6" s="24" t="n">
+        <v>55067.35</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>23.01</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>0.1953125</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>1.059520143</v>
+      </c>
+      <c r="F6" s="34">
+        <f>IF(D6="","",100*(1-D6))</f>
+        <v/>
+      </c>
+      <c r="G6" s="34">
+        <f>IF(E6="","",IF(E6&lt;=0,20,IF(E6&lt;5%,20+400*E6,IF(E6&lt;10%,40+400*(E6-5%),IF(E6&lt;15%,60+400*(E6-10%),IF(E6&lt;25%,80+200*(E6-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H6" s="34">
+        <f>IF(OR(F6="",G6=""),"",70%*F6+30%*G6)</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4444,7 +4477,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-23</t>
+          <t>Retrieved 2026-09-24</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-50.xlsx
+++ b/docs/downloads/indices/nifty-alpha-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>55067.35</v>
+        <v>55024.65</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>23.01</v>
+        <v>22.99</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2393.19209039548</v>
+        <v>2393.416702914311</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>1.059520142999616</v>
+        <v>1.059598937742356</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0434593654932638</v>
+        <v>0.04349717268377556</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>29.75</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>71197.46468926553</v>
+        <v>71204.14691170074</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2929161234245978</v>
+        <v>0.2940408873423226</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>41.96</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>100418.3401129944</v>
+        <v>100427.7648542845</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.8235549760973491</v>
+        <v>0.8251413658112225</v>
       </c>
     </row>
     <row r="16">
@@ -4214,7 +4214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4437,6 +4437,39 @@
       </c>
       <c r="I6">
         <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B7" s="24" t="n">
+        <v>55024.65</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>0.1953125</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>1.05959893774</v>
+      </c>
+      <c r="F7" s="34">
+        <f>IF(D7="","",100*(1-D7))</f>
+        <v/>
+      </c>
+      <c r="G7" s="34">
+        <f>IF(E7="","",IF(E7&lt;=0,20,IF(E7&lt;5%,20+400*E7,IF(E7&lt;10%,40+400*(E7-5%),IF(E7&lt;15%,60+400*(E7-10%),IF(E7&lt;25%,80+200*(E7-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H7" s="34">
+        <f>IF(OR(F7="",G7=""),"",70%*F7+30%*G7)</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4477,7 +4510,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-24</t>
+          <t>Retrieved 2026-09-25</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-50.xlsx
+++ b/docs/downloads/indices/nifty-alpha-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>55024.65</v>
+        <v>53779</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.99</v>
+        <v>22.47</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2393.416702914311</v>
+        <v>2393.368936359591</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>1.059598937742356</v>
+        <v>1.059729629894741</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04349717268377556</v>
+        <v>0.04450378282153983</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>29.75</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>71204.14691170074</v>
+        <v>71202.72585669781</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2940408873423226</v>
+        <v>0.3239875389408098</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>41.96</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>100427.7648542845</v>
+        <v>100425.7605696484</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.8251413658112225</v>
+        <v>0.8673787271918116</v>
       </c>
     </row>
     <row r="16">
@@ -4214,7 +4214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4470,6 +4470,39 @@
       </c>
       <c r="I7">
         <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>53779</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>22.47</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>0.1953125</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>1.05972962989</v>
+      </c>
+      <c r="F8" s="34">
+        <f>IF(D8="","",100*(1-D8))</f>
+        <v/>
+      </c>
+      <c r="G8" s="34">
+        <f>IF(E8="","",IF(E8&lt;=0,20,IF(E8&lt;5%,20+400*E8,IF(E8&lt;10%,40+400*(E8-5%),IF(E8&lt;15%,60+400*(E8-10%),IF(E8&lt;25%,80+200*(E8-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H8" s="34">
+        <f>IF(OR(F8="",G8=""),"",70%*F8+30%*G8)</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4510,7 +4543,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-25</t>
+          <t>Retrieved 2026-09-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-50.xlsx
+++ b/docs/downloads/indices/nifty-alpha-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>53779</v>
+        <v>53519.45</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.47</v>
+        <v>22.37</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2393.368936359591</v>
+        <v>2392.465355386678</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>1.059729629894741</v>
+        <v>1.058854105626479</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04450378282153983</v>
+        <v>0.04470272686633885</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>29.75</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>71202.72585669781</v>
+        <v>71175.84432275368</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.3239875389408098</v>
+        <v>0.3299061242735806</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>41.96</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>100425.7605696484</v>
+        <v>100387.846312025</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.8673787271918116</v>
+        <v>0.8757264193115779</v>
       </c>
     </row>
     <row r="16">
@@ -4214,7 +4214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4503,6 +4503,39 @@
       </c>
       <c r="I8">
         <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B9" s="24" t="n">
+        <v>53519.45</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>22.37</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>0.1953125</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>1.05885410563</v>
+      </c>
+      <c r="F9" s="34">
+        <f>IF(D9="","",100*(1-D9))</f>
+        <v/>
+      </c>
+      <c r="G9" s="34">
+        <f>IF(E9="","",IF(E9&lt;=0,20,IF(E9&lt;5%,20+400*E9,IF(E9&lt;10%,40+400*(E9-5%),IF(E9&lt;15%,60+400*(E9-10%),IF(E9&lt;25%,80+200*(E9-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H9" s="34">
+        <f>IF(OR(F9="",G9=""),"",70%*F9+30%*G9)</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4543,7 +4576,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-28</t>
+          <t>Retrieved 2026-09-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -4693,17 +4726,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Amber Enterprises India Ltd.</t>
+          <t>Apar Industries Ltd.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AMBER</t>
+          <t>APARINDS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Consumer Durables</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -4713,17 +4746,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Anand Rathi Wealth Ltd.</t>
+          <t>Ashok Leyland Ltd.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ANANDRATHI</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -4733,17 +4766,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Apar Industries Ltd.</t>
+          <t>Ather Energy Ltd.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>APARINDS</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -4753,17 +4786,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ashok Leyland Ltd.</t>
+          <t>AU Small Finance Bank Ltd.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4773,17 +4806,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ather Energy Ltd.</t>
+          <t>Bank of India</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>BANKINDIA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4793,17 +4826,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AU Small Finance Bank Ltd.</t>
+          <t>Bharat Forge Ltd.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -4813,17 +4846,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bank of India</t>
+          <t>Bharat Heavy Electricals Ltd.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BANKINDIA</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -4833,17 +4866,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bharat Forge Ltd.</t>
+          <t>BSE Ltd.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4853,17 +4886,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bharat Heavy Electricals Ltd.</t>
+          <t>Canara Bank</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4873,17 +4906,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BSE Ltd.</t>
+          <t>Cummins India Ltd.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>CUMMINSIND</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -4893,17 +4926,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Canara Bank</t>
+          <t>Cupid Ltd.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>CUPID</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -4913,17 +4946,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cummins India Ltd.</t>
+          <t>Eicher Motors Ltd.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -4933,17 +4966,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Delhivery Ltd.</t>
+          <t>Federal Bank Ltd.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DELHIVERY</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -4953,17 +4986,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Eicher Motors Ltd.</t>
+          <t>FSN E-Commerce Ventures Ltd.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>NYKAA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Consumer Services</t>
         </is>
       </c>
     </row>
@@ -4973,17 +5006,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Federal Bank Ltd.</t>
+          <t>GE Vernova T&amp;D India Ltd.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>GVT&amp;D</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -4993,12 +5026,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fortis Healthcare Ltd.</t>
+          <t>Glenmark Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>GLENMARK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5013,17 +5046,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FSN E-Commerce Ventures Ltd.</t>
+          <t>HFCL Ltd.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>HFCL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Consumer Services</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -5033,17 +5066,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GE Vernova T&amp;D India Ltd.</t>
+          <t>Hindalco Industries Ltd.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GVT&amp;D</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -5053,17 +5086,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Glenmark Pharmaceuticals Ltd.</t>
+          <t>Hindustan Copper Ltd.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GLENMARK</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -5073,17 +5106,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HDFC Asset Management Company Ltd.</t>
+          <t>Hitachi Energy India Ltd.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>HDFCAMC</t>
+          <t>POWERINDIA</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5093,17 +5126,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hindalco Industries Ltd.</t>
+          <t>IIFL Finance Ltd.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>IIFL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5113,17 +5146,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hindustan Copper Ltd.</t>
+          <t>Indian Bank</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5133,17 +5166,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Hitachi Energy India Ltd.</t>
+          <t>Karur Vysya Bank Ltd.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>POWERINDIA</t>
+          <t>KARURVYSYA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5153,17 +5186,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IIFL Finance Ltd.</t>
+          <t>Kirloskar Oil Eng Ltd.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IIFL</t>
+          <t>KIRLOSENG</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5206,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Indian Bank</t>
+          <t>L&amp;T Finance Ltd.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>LTF</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5193,17 +5226,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Karur Vysya Bank Ltd.</t>
+          <t>Laurus Labs Ltd.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>KARURVYSYA</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
     </row>
@@ -5213,12 +5246,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>L&amp;T Finance Ltd.</t>
+          <t>Manappuram Finance Ltd.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LTF</t>
+          <t>MANAPPURAM</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5233,17 +5266,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Laurus Labs Ltd.</t>
+          <t>MTAR Technologies Ltd.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5253,12 +5286,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Manappuram Finance Ltd.</t>
+          <t>Multi Commodity Exchange of India Ltd.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MANAPPURAM</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5273,17 +5306,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Max Financial Services Ltd.</t>
+          <t>National Aluminium Co. Ltd.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -5293,17 +5326,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Multi Commodity Exchange of India Ltd.</t>
+          <t>Navin Fluorine International Ltd.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5346,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Muthoot Finance Ltd.</t>
+          <t>One 97 Communications Ltd.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5333,17 +5366,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>National Aluminium Co. Ltd.</t>
+          <t>Polycab India Ltd.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5353,17 +5386,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Navin Fluorine International Ltd.</t>
+          <t>Radico Khaitan Ltd</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NAVINFLUOR</t>
+          <t>RADICO</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Fast Moving Consumer Goods</t>
         </is>
       </c>
     </row>
@@ -5373,12 +5406,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>One 97 Communications Ltd.</t>
+          <t>RBL Bank Ltd.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5393,17 +5426,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Polycab India Ltd.</t>
+          <t>Shriram Finance Ltd.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Capital Goods</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5413,17 +5446,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Radico Khaitan Ltd</t>
+          <t>Solar Industries India Ltd.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>RADICO</t>
+          <t>SOLARINDS</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Fast Moving Consumer Goods</t>
+          <t>Chemicals</t>
         </is>
       </c>
     </row>
@@ -5433,12 +5466,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RBL Bank Ltd.</t>
+          <t>State Bank of India</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5453,17 +5486,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Shriram Finance Ltd.</t>
+          <t>Steel Authority of India Ltd.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -5473,17 +5506,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Solar Industries India Ltd.</t>
+          <t>Sterlite Technologies Ltd.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SOLARINDS</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -5493,17 +5526,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>State Bank of India</t>
+          <t>TD Power Systems Ltd.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>
@@ -5513,17 +5546,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Steel Authority of India Ltd.</t>
+          <t>TVS Motor Company Ltd.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>TVSMOTOR</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Automobile and Auto Components</t>
         </is>
       </c>
     </row>
@@ -5533,17 +5566,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TVS Motor Company Ltd.</t>
+          <t>Union Bank of India</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TVSMOTOR</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Automobile and Auto Components</t>
+          <t>Financial Services</t>
         </is>
       </c>
     </row>
@@ -5553,17 +5586,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Union Bank of India</t>
+          <t>Vedanta Ltd.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>VEDL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
     </row>
@@ -5573,17 +5606,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Vedanta Ltd.</t>
+          <t>Vodafone Idea Ltd.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>VEDL</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Telecommunication</t>
         </is>
       </c>
     </row>
@@ -5593,17 +5626,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Vodafone Idea Ltd.</t>
+          <t>Welspun Corp Ltd.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>WELCORP</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Telecommunication</t>
+          <t>Capital Goods</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-alpha-50.xlsx
+++ b/docs/downloads/indices/nifty-alpha-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>53519.45</v>
+        <v>54079.15</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>22.37</v>
+        <v>27.55</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.1953125</v>
+        <v>0.3692307692307693</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2392.465355386678</v>
+        <v>1962.94555353902</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>1.058854105626479</v>
+        <v>0.6264227021633593</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04470272686633885</v>
+        <v>0.03629764065335753</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>80.46875</v>
+        <v>63.07692307692307</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>86.328125</v>
+        <v>74.15384615384615</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>29.75</v>
+        <v>29.58428571428571</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>71175.84432275368</v>
+        <v>58072.34209748509</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.3299061242735806</v>
+        <v>0.07383977184340162</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>41.96</v>
+        <v>41.91</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>100387.846312025</v>
+        <v>82267.04814882032</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.8757264193115779</v>
+        <v>0.5212341197822141</v>
       </c>
     </row>
     <row r="16">
@@ -818,14 +818,14 @@
         <v>0.6552149306854191</v>
       </c>
       <c r="D18" s="30" t="n">
-        <v>0.1724472302215659</v>
+        <v>0.1526438947529591</v>
       </c>
       <c r="E18" s="30" t="n">
         <v>0.268370171373254</v>
       </c>
       <c r="F18" s="30" t="n"/>
       <c r="G18" s="30" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="19">
@@ -846,7 +846,9 @@
       <c r="E19" s="30" t="n">
         <v>0.2777889235479469</v>
       </c>
-      <c r="F19" s="30" t="n"/>
+      <c r="F19" s="30" t="n">
+        <v>0.1904120166906922</v>
+      </c>
       <c r="G19" s="30" t="n">
         <v>0</v>
       </c>
@@ -858,7 +860,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C20" s="30" t="n">
         <v>0.193638156564597</v>
@@ -886,13 +888,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="30" t="n">
-        <v>-0.03296630441988901</v>
+        <v>0.03714383685575023</v>
       </c>
       <c r="D21" s="30" t="n">
         <v>0.2624408626493824</v>
       </c>
       <c r="E21" s="30" t="n">
-        <v>0.3130642510298619</v>
+        <v>0.3110014600084163</v>
       </c>
       <c r="F21" s="30" t="n">
         <v>0.1783410127390987</v>
@@ -940,7 +942,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26">
@@ -950,7 +952,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27">
@@ -973,7 +975,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2288,6 +2290,25 @@
       </c>
       <c r="E66" s="20">
         <f>IFERROR(1/C66,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B67" s="24" t="n">
+        <v>54079.15</v>
+      </c>
+      <c r="C67" s="25" t="n">
+        <v>27.55</v>
+      </c>
+      <c r="D67" s="32">
+        <f>IFERROR(B67/C67,"")</f>
+        <v/>
+      </c>
+      <c r="E67" s="20">
+        <f>IFERROR(1/C67,"")</f>
         <v/>
       </c>
     </row>
@@ -2304,7 +2325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2404,7 +2425,7 @@
       </c>
       <c r="F2" s="30" t="n"/>
       <c r="G2" s="30">
-        <f>IF(C2="","",(COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,C2)+1)/2)/COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C2="","",(COUNTIFS($D$2:$D$45,D2,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$45,D2,$C$2:$C$45,C2)+1)/2)/COUNTIFS($D$2:$D$45,D2,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H2">
@@ -2449,7 +2470,7 @@
       </c>
       <c r="F3" s="30" t="n"/>
       <c r="G3" s="30">
-        <f>IF(C3="","",(COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,C3)+1)/2)/COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C3="","",(COUNTIFS($D$2:$D$45,D3,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$45,D3,$C$2:$C$45,C3)+1)/2)/COUNTIFS($D$2:$D$45,D3,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H3">
@@ -2494,7 +2515,7 @@
       </c>
       <c r="F4" s="30" t="n"/>
       <c r="G4" s="30">
-        <f>IF(C4="","",(COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,C4)+1)/2)/COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C4="","",(COUNTIFS($D$2:$D$45,D4,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$45,D4,$C$2:$C$45,C4)+1)/2)/COUNTIFS($D$2:$D$45,D4,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H4">
@@ -2539,7 +2560,7 @@
       </c>
       <c r="F5" s="30" t="n"/>
       <c r="G5" s="30">
-        <f>IF(C5="","",(COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,C5)+1)/2)/COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C5="","",(COUNTIFS($D$2:$D$45,D5,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$45,D5,$C$2:$C$45,C5)+1)/2)/COUNTIFS($D$2:$D$45,D5,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H5">
@@ -2558,7 +2579,10 @@
         <f>IFERROR((B25/B5)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L5" s="30" t="n"/>
+      <c r="L5" s="30">
+        <f>IFERROR((B45/B5)^(1/10)-1,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="31" t="n">
@@ -2584,7 +2608,7 @@
         <v/>
       </c>
       <c r="G6" s="30">
-        <f>IF(C6="","",(COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,C6)+1)/2)/COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C6="","",(COUNTIFS($D$2:$D$45,D6,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$45,D6,$C$2:$C$45,C6)+1)/2)/COUNTIFS($D$2:$D$45,D6,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H6">
@@ -2629,7 +2653,7 @@
         <v/>
       </c>
       <c r="G7" s="30">
-        <f>IF(C7="","",(COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,C7)+1)/2)/COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C7="","",(COUNTIFS($D$2:$D$45,D7,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$45,D7,$C$2:$C$45,C7)+1)/2)/COUNTIFS($D$2:$D$45,D7,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H7">
@@ -2674,7 +2698,7 @@
         <v/>
       </c>
       <c r="G8" s="30">
-        <f>IF(C8="","",(COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,C8)+1)/2)/COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C8="","",(COUNTIFS($D$2:$D$45,D8,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$45,D8,$C$2:$C$45,C8)+1)/2)/COUNTIFS($D$2:$D$45,D8,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H8">
@@ -2719,7 +2743,7 @@
         <v/>
       </c>
       <c r="G9" s="30">
-        <f>IF(C9="","",(COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,C9)+1)/2)/COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C9="","",(COUNTIFS($D$2:$D$45,D9,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$45,D9,$C$2:$C$45,C9)+1)/2)/COUNTIFS($D$2:$D$45,D9,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H9">
@@ -2764,7 +2788,7 @@
         <v/>
       </c>
       <c r="G10" s="30">
-        <f>IF(C10="","",(COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,C10)+1)/2)/COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C10="","",(COUNTIFS($D$2:$D$45,D10,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$45,D10,$C$2:$C$45,C10)+1)/2)/COUNTIFS($D$2:$D$45,D10,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H10">
@@ -2809,7 +2833,7 @@
         <v/>
       </c>
       <c r="G11" s="30">
-        <f>IF(C11="","",(COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,C11)+1)/2)/COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C11="","",(COUNTIFS($D$2:$D$45,D11,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$45,D11,$C$2:$C$45,C11)+1)/2)/COUNTIFS($D$2:$D$45,D11,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H11">
@@ -2854,7 +2878,7 @@
         <v/>
       </c>
       <c r="G12" s="30">
-        <f>IF(C12="","",(COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,C12)+1)/2)/COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C12="","",(COUNTIFS($D$2:$D$45,D12,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$45,D12,$C$2:$C$45,C12)+1)/2)/COUNTIFS($D$2:$D$45,D12,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H12">
@@ -2899,7 +2923,7 @@
         <v/>
       </c>
       <c r="G13" s="30">
-        <f>IF(C13="","",(COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,C13)+1)/2)/COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C13="","",(COUNTIFS($D$2:$D$45,D13,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$45,D13,$C$2:$C$45,C13)+1)/2)/COUNTIFS($D$2:$D$45,D13,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H13">
@@ -2944,7 +2968,7 @@
         <v/>
       </c>
       <c r="G14" s="30">
-        <f>IF(C14="","",(COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,C14)+1)/2)/COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C14="","",(COUNTIFS($D$2:$D$45,D14,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$45,D14,$C$2:$C$45,C14)+1)/2)/COUNTIFS($D$2:$D$45,D14,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H14">
@@ -2989,7 +3013,7 @@
         <v/>
       </c>
       <c r="G15" s="30">
-        <f>IF(C15="","",(COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,C15)+1)/2)/COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C15="","",(COUNTIFS($D$2:$D$45,D15,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$45,D15,$C$2:$C$45,C15)+1)/2)/COUNTIFS($D$2:$D$45,D15,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H15">
@@ -3034,7 +3058,7 @@
         <v/>
       </c>
       <c r="G16" s="30">
-        <f>IF(C16="","",(COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,C16)+1)/2)/COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C16="","",(COUNTIFS($D$2:$D$45,D16,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$45,D16,$C$2:$C$45,C16)+1)/2)/COUNTIFS($D$2:$D$45,D16,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H16">
@@ -3079,7 +3103,7 @@
         <v/>
       </c>
       <c r="G17" s="30">
-        <f>IF(C17="","",(COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,C17)+1)/2)/COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C17="","",(COUNTIFS($D$2:$D$45,D17,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$45,D17,$C$2:$C$45,C17)+1)/2)/COUNTIFS($D$2:$D$45,D17,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H17">
@@ -3124,7 +3148,7 @@
         <v/>
       </c>
       <c r="G18" s="30">
-        <f>IF(C18="","",(COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,C18)+1)/2)/COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C18="","",(COUNTIFS($D$2:$D$45,D18,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$45,D18,$C$2:$C$45,C18)+1)/2)/COUNTIFS($D$2:$D$45,D18,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H18">
@@ -3169,7 +3193,7 @@
         <v/>
       </c>
       <c r="G19" s="30">
-        <f>IF(C19="","",(COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,C19)+1)/2)/COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C19="","",(COUNTIFS($D$2:$D$45,D19,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$45,D19,$C$2:$C$45,C19)+1)/2)/COUNTIFS($D$2:$D$45,D19,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H19">
@@ -3214,7 +3238,7 @@
         <v/>
       </c>
       <c r="G20" s="30">
-        <f>IF(C20="","",(COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,C20)+1)/2)/COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C20="","",(COUNTIFS($D$2:$D$45,D20,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$45,D20,$C$2:$C$45,C20)+1)/2)/COUNTIFS($D$2:$D$45,D20,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H20">
@@ -3257,7 +3281,7 @@
         <v/>
       </c>
       <c r="G21" s="30">
-        <f>IF(C21="","",(COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,C21)+1)/2)/COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C21="","",(COUNTIFS($D$2:$D$45,D21,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$45,D21,$C$2:$C$45,C21)+1)/2)/COUNTIFS($D$2:$D$45,D21,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H21">
@@ -3300,7 +3324,7 @@
         <v/>
       </c>
       <c r="G22" s="30">
-        <f>IF(C22="","",(COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,C22)+1)/2)/COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C22="","",(COUNTIFS($D$2:$D$45,D22,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$45,D22,$C$2:$C$45,C22)+1)/2)/COUNTIFS($D$2:$D$45,D22,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H22">
@@ -3343,7 +3367,7 @@
         <v/>
       </c>
       <c r="G23" s="30">
-        <f>IF(C23="","",(COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,C23)+1)/2)/COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C23="","",(COUNTIFS($D$2:$D$45,D23,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$45,D23,$C$2:$C$45,C23)+1)/2)/COUNTIFS($D$2:$D$45,D23,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H23">
@@ -3388,7 +3412,7 @@
         <v/>
       </c>
       <c r="G24" s="30">
-        <f>IF(C24="","",(COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,C24)+1)/2)/COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C24="","",(COUNTIFS($D$2:$D$45,D24,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$45,D24,$C$2:$C$45,C24)+1)/2)/COUNTIFS($D$2:$D$45,D24,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H24">
@@ -3433,7 +3457,7 @@
         <v/>
       </c>
       <c r="G25" s="30">
-        <f>IF(C25="","",(COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,C25)+1)/2)/COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C25="","",(COUNTIFS($D$2:$D$45,D25,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$45,D25,$C$2:$C$45,C25)+1)/2)/COUNTIFS($D$2:$D$45,D25,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H25">
@@ -3448,7 +3472,10 @@
         <f>IFERROR((B37/B25)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K25" s="30" t="n"/>
+      <c r="K25" s="30">
+        <f>IFERROR((B45/B25)^(1/5)-1,"")</f>
+        <v/>
+      </c>
       <c r="L25" s="30" t="n"/>
     </row>
     <row r="26">
@@ -3475,7 +3502,7 @@
         <v/>
       </c>
       <c r="G26" s="30">
-        <f>IF(C26="","",(COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,C26)+1)/2)/COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C26="","",(COUNTIFS($D$2:$D$45,D26,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$45,D26,$C$2:$C$45,C26)+1)/2)/COUNTIFS($D$2:$D$45,D26,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H26">
@@ -3517,7 +3544,7 @@
         <v/>
       </c>
       <c r="G27" s="30">
-        <f>IF(C27="","",(COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,C27)+1)/2)/COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C27="","",(COUNTIFS($D$2:$D$45,D27,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$45,D27,$C$2:$C$45,C27)+1)/2)/COUNTIFS($D$2:$D$45,D27,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H27">
@@ -3559,7 +3586,7 @@
         <v/>
       </c>
       <c r="G28" s="30">
-        <f>IF(C28="","",(COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,C28)+1)/2)/COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C28="","",(COUNTIFS($D$2:$D$45,D28,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$45,D28,$C$2:$C$45,C28)+1)/2)/COUNTIFS($D$2:$D$45,D28,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H28">
@@ -3601,7 +3628,7 @@
         <v/>
       </c>
       <c r="G29" s="30">
-        <f>IF(C29="","",(COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,C29)+1)/2)/COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C29="","",(COUNTIFS($D$2:$D$45,D29,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$45,D29,$C$2:$C$45,C29)+1)/2)/COUNTIFS($D$2:$D$45,D29,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H29">
@@ -3643,7 +3670,7 @@
         <v/>
       </c>
       <c r="G30" s="30">
-        <f>IF(C30="","",(COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,C30)+1)/2)/COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C30="","",(COUNTIFS($D$2:$D$45,D30,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$45,D30,$C$2:$C$45,C30)+1)/2)/COUNTIFS($D$2:$D$45,D30,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H30">
@@ -3685,7 +3712,7 @@
         <v/>
       </c>
       <c r="G31" s="30">
-        <f>IF(C31="","",(COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,C31)+1)/2)/COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C31="","",(COUNTIFS($D$2:$D$45,D31,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$45,D31,$C$2:$C$45,C31)+1)/2)/COUNTIFS($D$2:$D$45,D31,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H31">
@@ -3727,7 +3754,7 @@
         <v/>
       </c>
       <c r="G32" s="30">
-        <f>IF(C32="","",(COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,C32)+1)/2)/COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C32="","",(COUNTIFS($D$2:$D$45,D32,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$45,D32,$C$2:$C$45,C32)+1)/2)/COUNTIFS($D$2:$D$45,D32,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H32">
@@ -3769,7 +3796,7 @@
         <v/>
       </c>
       <c r="G33" s="30">
-        <f>IF(C33="","",(COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,C33)+1)/2)/COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C33="","",(COUNTIFS($D$2:$D$45,D33,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$45,D33,$C$2:$C$45,C33)+1)/2)/COUNTIFS($D$2:$D$45,D33,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H33">
@@ -3780,7 +3807,10 @@
         <f>IFERROR(B37/B33-1,"")</f>
         <v/>
       </c>
-      <c r="J33" s="30" t="n"/>
+      <c r="J33" s="30">
+        <f>IFERROR((B45/B33)^(1/3)-1,"")</f>
+        <v/>
+      </c>
       <c r="K33" s="30" t="n"/>
       <c r="L33" s="30" t="n"/>
     </row>
@@ -3808,7 +3838,7 @@
         <v/>
       </c>
       <c r="G34" s="30">
-        <f>IF(C34="","",(COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,C34)+1)/2)/COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C34="","",(COUNTIFS($D$2:$D$45,D34,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$45,D34,$C$2:$C$45,C34)+1)/2)/COUNTIFS($D$2:$D$45,D34,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H34">
@@ -3847,7 +3877,7 @@
         <v/>
       </c>
       <c r="G35" s="30">
-        <f>IF(C35="","",(COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,C35)+1)/2)/COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C35="","",(COUNTIFS($D$2:$D$45,D35,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$45,D35,$C$2:$C$45,C35)+1)/2)/COUNTIFS($D$2:$D$45,D35,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H35">
@@ -3886,7 +3916,7 @@
         <v/>
       </c>
       <c r="G36" s="30">
-        <f>IF(C36="","",(COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,C36)+1)/2)/COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C36="","",(COUNTIFS($D$2:$D$45,D36,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$45,D36,$C$2:$C$45,C36)+1)/2)/COUNTIFS($D$2:$D$45,D36,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H36">
@@ -3925,7 +3955,7 @@
         <v/>
       </c>
       <c r="G37" s="30">
-        <f>IF(C37="","",(COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,C37)+1)/2)/COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C37="","",(COUNTIFS($D$2:$D$45,D37,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$45,D37,$C$2:$C$45,C37)+1)/2)/COUNTIFS($D$2:$D$45,D37,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H37">
@@ -3964,7 +3994,7 @@
         <v/>
       </c>
       <c r="G38" s="30">
-        <f>IF(C38="","",(COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,C38)+1)/2)/COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C38="","",(COUNTIFS($D$2:$D$45,D38,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$45,D38,$C$2:$C$45,C38)+1)/2)/COUNTIFS($D$2:$D$45,D38,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H38">
@@ -4003,7 +4033,7 @@
         <v/>
       </c>
       <c r="G39" s="30">
-        <f>IF(C39="","",(COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,C39)+1)/2)/COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C39="","",(COUNTIFS($D$2:$D$45,D39,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$45,D39,$C$2:$C$45,C39)+1)/2)/COUNTIFS($D$2:$D$45,D39,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H39">
@@ -4042,7 +4072,7 @@
         <v/>
       </c>
       <c r="G40" s="30">
-        <f>IF(C40="","",(COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,C40)+1)/2)/COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C40="","",(COUNTIFS($D$2:$D$45,D40,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$45,D40,$C$2:$C$45,C40)+1)/2)/COUNTIFS($D$2:$D$45,D40,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H40">
@@ -4081,14 +4111,17 @@
         <v/>
       </c>
       <c r="G41" s="30">
-        <f>IF(C41="","",(COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,C41)+1)/2)/COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C41="","",(COUNTIFS($D$2:$D$45,D41,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$45,D41,$C$2:$C$45,C41)+1)/2)/COUNTIFS($D$2:$D$45,D41,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H41">
         <f>IF(G41="","",IF(G41&lt;=20%,"Q1 Cheapest",IF(G41&lt;=40%,"Q2",IF(G41&lt;=60%,"Q3",IF(G41&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I41" s="30" t="n"/>
+      <c r="I41" s="30">
+        <f>IFERROR(B45/B41-1,"")</f>
+        <v/>
+      </c>
       <c r="J41" s="30" t="n"/>
       <c r="K41" s="30" t="n"/>
       <c r="L41" s="30" t="n"/>
@@ -4117,7 +4150,7 @@
         <v/>
       </c>
       <c r="G42" s="30">
-        <f>IF(C42="","",(COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,C42)+1)/2)/COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C42="","",(COUNTIFS($D$2:$D$45,D42,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$45,D42,$C$2:$C$45,C42)+1)/2)/COUNTIFS($D$2:$D$45,D42,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H42">
@@ -4153,7 +4186,7 @@
         <v/>
       </c>
       <c r="G43" s="30">
-        <f>IF(C43="","",(COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C43)+(COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,C43)+1)/2)/COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C43="","",(COUNTIFS($D$2:$D$45,D43,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C43)+(COUNTIFS($D$2:$D$45,D43,$C$2:$C$45,C43)+1)/2)/COUNTIFS($D$2:$D$45,D43,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H43">
@@ -4189,7 +4222,7 @@
         <v/>
       </c>
       <c r="G44" s="30">
-        <f>IF(C44="","",(COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C44)+(COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,C44)+1)/2)/COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C44="","",(COUNTIFS($D$2:$D$45,D44,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C44)+(COUNTIFS($D$2:$D$45,D44,$C$2:$C$45,C44)+1)/2)/COUNTIFS($D$2:$D$45,D44,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H44">
@@ -4200,6 +4233,42 @@
       <c r="J44" s="30" t="n"/>
       <c r="K44" s="30" t="n"/>
       <c r="L44" s="30" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B45" s="24" t="n">
+        <v>54079.15</v>
+      </c>
+      <c r="C45" s="25" t="n">
+        <v>27.55</v>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated</t>
+        </is>
+      </c>
+      <c r="E45" s="33">
+        <f>IFERROR(B45/C45,"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="30">
+        <f>IF(AND(D45=D41,E41&lt;&gt;""),E45/E41-1,"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="30">
+        <f>IF(C45="","",(COUNTIFS($D$2:$D$45,D45,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C45)+(COUNTIFS($D$2:$D$45,D45,$C$2:$C$45,C45)+1)/2)/COUNTIFS($D$2:$D$45,D45,$C$2:$C$45,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="H45">
+        <f>IF(G45="","",IF(G45&lt;=20%,"Q1 Cheapest",IF(G45&lt;=40%,"Q2",IF(G45&lt;=60%,"Q3",IF(G45&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
+        <v/>
+      </c>
+      <c r="I45" s="30" t="n"/>
+      <c r="J45" s="30" t="n"/>
+      <c r="K45" s="30" t="n"/>
+      <c r="L45" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -4214,7 +4283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4222,7 +4291,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
@@ -4536,6 +4605,39 @@
       </c>
       <c r="I9">
         <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B10" s="24" t="n">
+        <v>54079.15</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>27.55</v>
+      </c>
+      <c r="D10" s="26" t="n">
+        <v>0.369230769231</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>0.626422702163</v>
+      </c>
+      <c r="F10" s="34">
+        <f>IF(D10="","",100*(1-D10))</f>
+        <v/>
+      </c>
+      <c r="G10" s="34">
+        <f>IF(E10="","",IF(E10&lt;=0,20,IF(E10&lt;5%,20+400*E10,IF(E10&lt;10%,40+400*(E10-5%),IF(E10&lt;15%,60+400*(E10-10%),IF(E10&lt;25%,80+200*(E10-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H10" s="34">
+        <f>IF(OR(F10="",G10=""),"",70%*F10+30%*G10)</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4576,7 +4678,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-29</t>
+          <t>Retrieved 2026-09-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-50.xlsx
+++ b/docs/downloads/indices/nifty-alpha-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>54079.15</v>
+        <v>53855.85</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>27.55</v>
+        <v>27.44</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.3692307692307693</v>
+        <v>0.3615384615384615</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1962.94555353902</v>
+        <v>1962.676749271137</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.6264227021633593</v>
+        <v>0.6261018983066791</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03629764065335753</v>
+        <v>0.03644314868804664</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>63.07692307692307</v>
+        <v>63.84615384615384</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>74.15384615384615</v>
+        <v>74.69230769230768</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>29.58428571428571</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>58072.34209748509</v>
+        <v>58064.38971522282</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.07383977184340162</v>
+        <v>0.07814452311536857</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>41.91</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>82267.04814882032</v>
+        <v>82255.78256195334</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5212341197822141</v>
+        <v>0.5273323615160348</v>
       </c>
     </row>
     <row r="16">
@@ -4283,7 +4283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4638,6 +4638,39 @@
       </c>
       <c r="I10">
         <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B11" s="24" t="n">
+        <v>53855.85</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>27.44</v>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>0.361538461538</v>
+      </c>
+      <c r="E11" s="26" t="n">
+        <v>0.626101898307</v>
+      </c>
+      <c r="F11" s="34">
+        <f>IF(D11="","",100*(1-D11))</f>
+        <v/>
+      </c>
+      <c r="G11" s="34">
+        <f>IF(E11="","",IF(E11&lt;=0,20,IF(E11&lt;5%,20+400*E11,IF(E11&lt;10%,40+400*(E11-5%),IF(E11&lt;15%,60+400*(E11-10%),IF(E11&lt;25%,80+200*(E11-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H11" s="34">
+        <f>IF(OR(F11="",G11=""),"",70%*F11+30%*G11)</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4678,7 +4711,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-09-30</t>
+          <t>Retrieved 2026-10-01</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-50.xlsx
+++ b/docs/downloads/indices/nifty-alpha-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>53855.85</v>
+        <v>54448.6</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>27.44</v>
+        <v>27.74</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.3615384615384615</v>
+        <v>0.3769230769230769</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1962.676749271137</v>
+        <v>1962.819033886085</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.6261018983066791</v>
+        <v>0.6262556753992012</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03644314868804664</v>
+        <v>0.03604902667627975</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>63.84615384615384</v>
+        <v>62.30769230769231</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>74.69230769230768</v>
+        <v>73.61538461538461</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>29.58428571428571</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>58064.38971522282</v>
+        <v>58068.59910392419</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.07814452311536857</v>
+        <v>0.06648470491296732</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>41.91</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>82255.78256195334</v>
+        <v>82261.74571016582</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5273323615160348</v>
+        <v>0.510814708002884</v>
       </c>
     </row>
     <row r="16">
@@ -4283,7 +4283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4671,6 +4671,39 @@
       </c>
       <c r="I11">
         <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B12" s="24" t="n">
+        <v>54448.6</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>27.74</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>0.376923076923</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>0.626255675399</v>
+      </c>
+      <c r="F12" s="34">
+        <f>IF(D12="","",100*(1-D12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="34">
+        <f>IF(E12="","",IF(E12&lt;=0,20,IF(E12&lt;5%,20+400*E12,IF(E12&lt;10%,40+400*(E12-5%),IF(E12&lt;15%,60+400*(E12-10%),IF(E12&lt;25%,80+200*(E12-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H12" s="34">
+        <f>IF(OR(F12="",G12=""),"",70%*F12+30%*G12)</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4711,7 +4744,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-01</t>
+          <t>Retrieved 2026-10-05</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-50.xlsx
+++ b/docs/downloads/indices/nifty-alpha-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>54448.6</v>
+        <v>55418.2</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>27.74</v>
+        <v>28.23</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.3769230769230769</v>
+        <v>0.3923076923076923</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1962.819033886085</v>
+        <v>1963.095997166135</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.6262556753992012</v>
+        <v>0.6266645680027398</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03604902667627975</v>
+        <v>0.03542330853701735</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>62.30769230769231</v>
+        <v>60.76923076923077</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>73.61538461538461</v>
+        <v>72.53846153846155</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>29.58428571428571</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>58068.59910392419</v>
+        <v>58076.79286473356</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.06648470491296732</v>
+        <v>0.04797328070441775</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>41.91</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>82261.74571016582</v>
+        <v>82273.35324123272</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.510814708002884</v>
+        <v>0.4845908607863973</v>
       </c>
     </row>
     <row r="16">
@@ -4283,7 +4283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4704,6 +4704,39 @@
       </c>
       <c r="I12">
         <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B13" s="24" t="n">
+        <v>55418.2</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>28.23</v>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>0.392307692308</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>0.626664568003</v>
+      </c>
+      <c r="F13" s="34">
+        <f>IF(D13="","",100*(1-D13))</f>
+        <v/>
+      </c>
+      <c r="G13" s="34">
+        <f>IF(E13="","",IF(E13&lt;=0,20,IF(E13&lt;5%,20+400*E13,IF(E13&lt;10%,40+400*(E13-5%),IF(E13&lt;15%,60+400*(E13-10%),IF(E13&lt;25%,80+200*(E13-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H13" s="34">
+        <f>IF(OR(F13="",G13=""),"",70%*F13+30%*G13)</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4744,7 +4777,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-05</t>
+          <t>Retrieved 2026-10-06</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-50.xlsx
+++ b/docs/downloads/indices/nifty-alpha-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>55418.2</v>
+        <v>55676.95</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>28.23</v>
+        <v>28.36</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1963.095997166135</v>
+        <v>1963.221086036671</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.6266645680027398</v>
+        <v>0.6265307750704967</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03542330853701735</v>
+        <v>0.03526093088857546</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>29.58428571428571</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>58076.79286473356</v>
+        <v>58080.49352961918</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.04797328070441775</v>
+        <v>0.04316945395929883</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>41.91</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>82273.35324123272</v>
+        <v>82278.59571579688</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4845908607863973</v>
+        <v>0.4777856135401972</v>
       </c>
     </row>
     <row r="16">
@@ -4283,7 +4283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4737,6 +4737,39 @@
       </c>
       <c r="I13">
         <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B14" s="24" t="n">
+        <v>55676.95</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>28.36</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>0.392307692308</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>0.62653077507</v>
+      </c>
+      <c r="F14" s="34">
+        <f>IF(D14="","",100*(1-D14))</f>
+        <v/>
+      </c>
+      <c r="G14" s="34">
+        <f>IF(E14="","",IF(E14&lt;=0,20,IF(E14&lt;5%,20+400*E14,IF(E14&lt;10%,40+400*(E14-5%),IF(E14&lt;15%,60+400*(E14-10%),IF(E14&lt;25%,80+200*(E14-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H14" s="34">
+        <f>IF(OR(F14="",G14=""),"",70%*F14+30%*G14)</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4777,7 +4810,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-06</t>
+          <t>Retrieved 2026-10-07</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-50.xlsx
+++ b/docs/downloads/indices/nifty-alpha-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>55676.95</v>
+        <v>54595</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>28.36</v>
+        <v>27.81</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.3923076923076923</v>
+        <v>0.3769230769230769</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1963.221086036671</v>
+        <v>1963.14275440489</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.6265307750704967</v>
+        <v>0.6267297156652627</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03526093088857546</v>
+        <v>0.03595828838547285</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>60.76923076923077</v>
+        <v>62.30769230769231</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>72.53846153846155</v>
+        <v>73.61538461538461</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>29.58428571428571</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>58080.49352961918</v>
+        <v>58078.17614424411</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.04316945395929883</v>
+        <v>0.06380027739251037</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>41.91</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>82278.59571579688</v>
+        <v>82275.31283710896</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4777856135401972</v>
+        <v>0.5070118662351673</v>
       </c>
     </row>
     <row r="16">
@@ -4283,7 +4283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4770,6 +4770,39 @@
       </c>
       <c r="I14">
         <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B15" s="24" t="n">
+        <v>54595</v>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>27.81</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>0.376923076923</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>0.626729715665</v>
+      </c>
+      <c r="F15" s="34">
+        <f>IF(D15="","",100*(1-D15))</f>
+        <v/>
+      </c>
+      <c r="G15" s="34">
+        <f>IF(E15="","",IF(E15&lt;=0,20,IF(E15&lt;5%,20+400*E15,IF(E15&lt;10%,40+400*(E15-5%),IF(E15&lt;15%,60+400*(E15-10%),IF(E15&lt;25%,80+200*(E15-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H15" s="34">
+        <f>IF(OR(F15="",G15=""),"",70%*F15+30%*G15)</f>
+        <v/>
+      </c>
+      <c r="I15">
+        <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4810,7 +4843,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-07</t>
+          <t>Retrieved 2026-10-08</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-50.xlsx
+++ b/docs/downloads/indices/nifty-alpha-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>54595</v>
+        <v>55339.9</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>27.81</v>
+        <v>28.19</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.3769230769230769</v>
+        <v>0.3923076923076923</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1963.14275440489</v>
+        <v>1963.103937566513</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.6267297156652627</v>
+        <v>0.6265167693247793</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03595828838547285</v>
+        <v>0.0354735721887194</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>62.30769230769231</v>
+        <v>60.76923076923077</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>73.61538461538461</v>
+        <v>72.53846153846155</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>29.58428571428571</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>58078.17614424411</v>
+        <v>58077.02777580702</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.06380027739251037</v>
+        <v>0.04946029493741433</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>41.91</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>82275.31283710896</v>
+        <v>82273.68602341255</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5070118662351673</v>
+        <v>0.4866974104292301</v>
       </c>
     </row>
     <row r="16">
@@ -4283,7 +4283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4803,6 +4803,39 @@
       </c>
       <c r="I15">
         <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B16" s="24" t="n">
+        <v>55339.9</v>
+      </c>
+      <c r="C16" s="25" t="n">
+        <v>28.19</v>
+      </c>
+      <c r="D16" s="26" t="n">
+        <v>0.392307692308</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>0.626516769325</v>
+      </c>
+      <c r="F16" s="34">
+        <f>IF(D16="","",100*(1-D16))</f>
+        <v/>
+      </c>
+      <c r="G16" s="34">
+        <f>IF(E16="","",IF(E16&lt;=0,20,IF(E16&lt;5%,20+400*E16,IF(E16&lt;10%,40+400*(E16-5%),IF(E16&lt;15%,60+400*(E16-10%),IF(E16&lt;25%,80+200*(E16-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H16" s="34">
+        <f>IF(OR(F16="",G16=""),"",70%*F16+30%*G16)</f>
+        <v/>
+      </c>
+      <c r="I16">
+        <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4843,7 +4876,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-08</t>
+          <t>Retrieved 2026-10-09</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-50.xlsx
+++ b/docs/downloads/indices/nifty-alpha-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>55339.9</v>
+        <v>55671.95</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>28.19</v>
+        <v>28.36</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1963.103937566513</v>
+        <v>1963.044781382228</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.6265167693247793</v>
+        <v>0.6263120609102213</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0354735721887194</v>
+        <v>0.03526093088857546</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>29.58428571428571</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>58077.02777580702</v>
+        <v>58075.27768234938</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.04946029493741433</v>
+        <v>0.04316945395929861</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>41.91</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>82273.68602341255</v>
+        <v>82271.20678772918</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4866974104292301</v>
+        <v>0.4777856135401974</v>
       </c>
     </row>
     <row r="16">
@@ -4283,7 +4283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4836,6 +4836,39 @@
       </c>
       <c r="I16">
         <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B17" s="24" t="n">
+        <v>55671.95</v>
+      </c>
+      <c r="C17" s="25" t="n">
+        <v>28.36</v>
+      </c>
+      <c r="D17" s="26" t="n">
+        <v>0.392307692308</v>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>0.62631206091</v>
+      </c>
+      <c r="F17" s="34">
+        <f>IF(D17="","",100*(1-D17))</f>
+        <v/>
+      </c>
+      <c r="G17" s="34">
+        <f>IF(E17="","",IF(E17&lt;=0,20,IF(E17&lt;5%,20+400*E17,IF(E17&lt;10%,40+400*(E17-5%),IF(E17&lt;15%,60+400*(E17-10%),IF(E17&lt;25%,80+200*(E17-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H17" s="34">
+        <f>IF(OR(F17="",G17=""),"",70%*F17+30%*G17)</f>
+        <v/>
+      </c>
+      <c r="I17">
+        <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4876,7 +4909,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-09</t>
+          <t>Retrieved 2026-10-12</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-50.xlsx
+++ b/docs/downloads/indices/nifty-alpha-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>55671.95</v>
+        <v>55337.55</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>28.36</v>
+        <v>28.15</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1963.044781382228</v>
+        <v>1965.809946714032</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.6263120609102213</v>
+        <v>0.6286386198597989</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03526093088857546</v>
+        <v>0.03552397868561279</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>29.58428571428571</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>58075.27768234938</v>
+        <v>58157.08312357269</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.04316945395929861</v>
+        <v>0.05095153514336448</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>41.91</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>82271.20678772918</v>
+        <v>82387.09486678508</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4777856135401974</v>
+        <v>0.4888099467140319</v>
       </c>
     </row>
     <row r="16">
@@ -4283,7 +4283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4869,6 +4869,39 @@
       </c>
       <c r="I17">
         <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B18" s="24" t="n">
+        <v>55337.55</v>
+      </c>
+      <c r="C18" s="25" t="n">
+        <v>28.15</v>
+      </c>
+      <c r="D18" s="26" t="n">
+        <v>0.392307692308</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>0.62863861986</v>
+      </c>
+      <c r="F18" s="34">
+        <f>IF(D18="","",100*(1-D18))</f>
+        <v/>
+      </c>
+      <c r="G18" s="34">
+        <f>IF(E18="","",IF(E18&lt;=0,20,IF(E18&lt;5%,20+400*E18,IF(E18&lt;10%,40+400*(E18-5%),IF(E18&lt;15%,60+400*(E18-10%),IF(E18&lt;25%,80+200*(E18-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H18" s="34">
+        <f>IF(OR(F18="",G18=""),"",70%*F18+30%*G18)</f>
+        <v/>
+      </c>
+      <c r="I18">
+        <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4909,7 +4942,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-12</t>
+          <t>Retrieved 2026-10-13</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-50.xlsx
+++ b/docs/downloads/indices/nifty-alpha-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>55337.55</v>
+        <v>54912.4</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>28.15</v>
+        <v>27.93</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.3923076923076923</v>
+        <v>0.3769230769230769</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1965.809946714032</v>
+        <v>1966.072323666309</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.6286386198597989</v>
+        <v>0.6288939833002332</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03552397868561279</v>
+        <v>0.03580379520229144</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>60.76923076923077</v>
+        <v>62.30769230769231</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>72.53846153846155</v>
+        <v>73.61538461538461</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>29.58428571428571</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>58157.08312357269</v>
+        <v>58164.84535829369</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.05095153514336448</v>
+        <v>0.059229706920362</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>41.91</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>82387.09486678508</v>
+        <v>82398.09108485498</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.4888099467140319</v>
+        <v>0.5005370569280341</v>
       </c>
     </row>
     <row r="16">
@@ -4283,7 +4283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4902,6 +4902,39 @@
       </c>
       <c r="I18">
         <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B19" s="24" t="n">
+        <v>54912.4</v>
+      </c>
+      <c r="C19" s="25" t="n">
+        <v>27.93</v>
+      </c>
+      <c r="D19" s="26" t="n">
+        <v>0.376923076923</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <v>0.6288939833</v>
+      </c>
+      <c r="F19" s="34">
+        <f>IF(D19="","",100*(1-D19))</f>
+        <v/>
+      </c>
+      <c r="G19" s="34">
+        <f>IF(E19="","",IF(E19&lt;=0,20,IF(E19&lt;5%,20+400*E19,IF(E19&lt;10%,40+400*(E19-5%),IF(E19&lt;15%,60+400*(E19-10%),IF(E19&lt;25%,80+200*(E19-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H19" s="34">
+        <f>IF(OR(F19="",G19=""),"",70%*F19+30%*G19)</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4942,7 +4975,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-13</t>
+          <t>Retrieved 2026-10-14</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-50.xlsx
+++ b/docs/downloads/indices/nifty-alpha-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>54912.4</v>
+        <v>53751.45</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>27.93</v>
+        <v>27.26</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.3769230769230769</v>
+        <v>0.3461538461538461</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1966.072323666309</v>
+        <v>1971.806676449009</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.6288939833002332</v>
+        <v>0.6329534337291398</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03580379520229144</v>
+        <v>0.03668378576669112</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>62.30769230769231</v>
+        <v>65.38461538461539</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>73.61538461538461</v>
+        <v>75.76923076923077</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>29.58428571428571</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>58164.84535829369</v>
+        <v>58334.49208940362</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.059229706920362</v>
+        <v>0.08526359920343762</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>41.91</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>82398.09108485498</v>
+        <v>82638.41780997797</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5005370569280341</v>
+        <v>0.5374174614820246</v>
       </c>
     </row>
     <row r="16">
@@ -4283,7 +4283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4935,6 +4935,39 @@
       </c>
       <c r="I19">
         <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B20" s="24" t="n">
+        <v>53751.45</v>
+      </c>
+      <c r="C20" s="25" t="n">
+        <v>27.26</v>
+      </c>
+      <c r="D20" s="26" t="n">
+        <v>0.346153846154</v>
+      </c>
+      <c r="E20" s="26" t="n">
+        <v>0.632953433729</v>
+      </c>
+      <c r="F20" s="34">
+        <f>IF(D20="","",100*(1-D20))</f>
+        <v/>
+      </c>
+      <c r="G20" s="34">
+        <f>IF(E20="","",IF(E20&lt;=0,20,IF(E20&lt;5%,20+400*E20,IF(E20&lt;10%,40+400*(E20-5%),IF(E20&lt;15%,60+400*(E20-10%),IF(E20&lt;25%,80+200*(E20-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H20" s="34">
+        <f>IF(OR(F20="",G20=""),"",70%*F20+30%*G20)</f>
+        <v/>
+      </c>
+      <c r="I20">
+        <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4975,7 +5008,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-14</t>
+          <t>Retrieved 2026-10-15</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-50.xlsx
+++ b/docs/downloads/indices/nifty-alpha-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>53751.45</v>
+        <v>53846.55</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>27.26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.3461538461538461</v>
+        <v>0.3153846153846154</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1971.806676449009</v>
+        <v>1994.316666666667</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.6329534337291398</v>
+        <v>0.6492357716757169</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03668378576669112</v>
+        <v>0.03703703703703703</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>65.38461538461539</v>
+        <v>68.46153846153847</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>75.76923076923077</v>
+        <v>77.92307692307693</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>29.58428571428571</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>58334.49208940362</v>
+        <v>59000.43407142857</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.08526359920343762</v>
+        <v>0.09571428571428564</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>41.91</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>82638.41780997797</v>
+        <v>83581.8115</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5374174614820246</v>
+        <v>0.5522222222222222</v>
       </c>
     </row>
     <row r="16">
@@ -4283,7 +4283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4968,6 +4968,39 @@
       </c>
       <c r="I20">
         <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B21" s="24" t="n">
+        <v>53846.55</v>
+      </c>
+      <c r="C21" s="25" t="n">
+        <v>27</v>
+      </c>
+      <c r="D21" s="26" t="n">
+        <v>0.315384615385</v>
+      </c>
+      <c r="E21" s="26" t="n">
+        <v>0.649235771676</v>
+      </c>
+      <c r="F21" s="34">
+        <f>IF(D21="","",100*(1-D21))</f>
+        <v/>
+      </c>
+      <c r="G21" s="34">
+        <f>IF(E21="","",IF(E21&lt;=0,20,IF(E21&lt;5%,20+400*E21,IF(E21&lt;10%,40+400*(E21-5%),IF(E21&lt;15%,60+400*(E21-10%),IF(E21&lt;25%,80+200*(E21-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H21" s="34">
+        <f>IF(OR(F21="",G21=""),"",70%*F21+30%*G21)</f>
+        <v/>
+      </c>
+      <c r="I21">
+        <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5008,7 +5041,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-15</t>
+          <t>Retrieved 2026-10-16</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-50.xlsx
+++ b/docs/downloads/indices/nifty-alpha-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>53846.55</v>
+        <v>53699.95</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>27</v>
+        <v>26.83</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1994.316666666667</v>
+        <v>2001.489004845322</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.6492357716757169</v>
+        <v>0.655756711125888</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03703703703703703</v>
+        <v>0.03727171077152441</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>29.58428571428571</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>59000.43407142857</v>
+        <v>59212.6225733454</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.09571428571428564</v>
+        <v>0.1026569405249986</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>41.91</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>83581.8115</v>
+        <v>83882.40419306746</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5522222222222222</v>
+        <v>0.5620573984345882</v>
       </c>
     </row>
     <row r="16">
@@ -4283,7 +4283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5001,6 +5001,39 @@
       </c>
       <c r="I21">
         <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B22" s="24" t="n">
+        <v>53699.95</v>
+      </c>
+      <c r="C22" s="25" t="n">
+        <v>26.83</v>
+      </c>
+      <c r="D22" s="26" t="n">
+        <v>0.315384615385</v>
+      </c>
+      <c r="E22" s="26" t="n">
+        <v>0.655756711126</v>
+      </c>
+      <c r="F22" s="34">
+        <f>IF(D22="","",100*(1-D22))</f>
+        <v/>
+      </c>
+      <c r="G22" s="34">
+        <f>IF(E22="","",IF(E22&lt;=0,20,IF(E22&lt;5%,20+400*E22,IF(E22&lt;10%,40+400*(E22-5%),IF(E22&lt;15%,60+400*(E22-10%),IF(E22&lt;25%,80+200*(E22-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H22" s="34">
+        <f>IF(OR(F22="",G22=""),"",70%*F22+30%*G22)</f>
+        <v/>
+      </c>
+      <c r="I22">
+        <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5041,7 +5074,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-16</t>
+          <t>Retrieved 2026-10-19</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-50.xlsx
+++ b/docs/downloads/indices/nifty-alpha-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>53699.95</v>
+        <v>52417.75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>26.83</v>
+        <v>26.19</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.3153846153846154</v>
+        <v>0.2846153846153846</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2001.489004845322</v>
+        <v>2001.441389843452</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.655756711125888</v>
+        <v>0.6536155295578761</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03727171077152441</v>
+        <v>0.03818251240931653</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>68.46153846153847</v>
+        <v>71.53846153846153</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>77.92307692307693</v>
+        <v>80.07692307692307</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>29.58428571428571</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>59212.6225733454</v>
+        <v>59211.21391752577</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.1026569405249986</v>
+        <v>0.1296023564064801</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>41.91</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>83882.40419306746</v>
+        <v>83880.40864833906</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5620573984345882</v>
+        <v>0.6002290950744558</v>
       </c>
     </row>
     <row r="16">
@@ -4283,7 +4283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5034,6 +5034,39 @@
       </c>
       <c r="I22">
         <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B23" s="24" t="n">
+        <v>52417.75</v>
+      </c>
+      <c r="C23" s="25" t="n">
+        <v>26.19</v>
+      </c>
+      <c r="D23" s="26" t="n">
+        <v>0.284615384615</v>
+      </c>
+      <c r="E23" s="26" t="n">
+        <v>0.653615529558</v>
+      </c>
+      <c r="F23" s="34">
+        <f>IF(D23="","",100*(1-D23))</f>
+        <v/>
+      </c>
+      <c r="G23" s="34">
+        <f>IF(E23="","",IF(E23&lt;=0,20,IF(E23&lt;5%,20+400*E23,IF(E23&lt;10%,40+400*(E23-5%),IF(E23&lt;15%,60+400*(E23-10%),IF(E23&lt;25%,80+200*(E23-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H23" s="34">
+        <f>IF(OR(F23="",G23=""),"",70%*F23+30%*G23)</f>
+        <v/>
+      </c>
+      <c r="I23">
+        <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5074,7 +5107,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-19</t>
+          <t>Retrieved 2026-10-21</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-50.xlsx
+++ b/docs/downloads/indices/nifty-alpha-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>52417.75</v>
+        <v>51352</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>26.19</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.2846153846153846</v>
+        <v>0.2692307692307692</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2001.441389843452</v>
+        <v>2029.723320158103</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.6536155295578761</v>
+        <v>0.6769824087537935</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03818251240931653</v>
+        <v>0.03952569169960474</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>71.53846153846153</v>
+        <v>73.07692307692308</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>80.07692307692307</v>
+        <v>81.15384615384616</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>29.58428571428571</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>59211.21391752577</v>
+        <v>60047.91462450592</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.1296023564064801</v>
+        <v>0.169339356295878</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>41.91</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>83880.40864833906</v>
+        <v>85065.70434782607</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.6002290950744558</v>
+        <v>0.6565217391304345</v>
       </c>
     </row>
     <row r="16">
@@ -4283,7 +4283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5067,6 +5067,39 @@
       </c>
       <c r="I23">
         <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B24" s="24" t="n">
+        <v>51352</v>
+      </c>
+      <c r="C24" s="25" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="D24" s="26" t="n">
+        <v>0.269230769231</v>
+      </c>
+      <c r="E24" s="26" t="n">
+        <v>0.676982408754</v>
+      </c>
+      <c r="F24" s="34">
+        <f>IF(D24="","",100*(1-D24))</f>
+        <v/>
+      </c>
+      <c r="G24" s="34">
+        <f>IF(E24="","",IF(E24&lt;=0,20,IF(E24&lt;5%,20+400*E24,IF(E24&lt;10%,40+400*(E24-5%),IF(E24&lt;15%,60+400*(E24-10%),IF(E24&lt;25%,80+200*(E24-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H24" s="34">
+        <f>IF(OR(F24="",G24=""),"",70%*F24+30%*G24)</f>
+        <v/>
+      </c>
+      <c r="I24">
+        <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5107,7 +5140,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-21</t>
+          <t>Retrieved 2026-10-22</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-50.xlsx
+++ b/docs/downloads/indices/nifty-alpha-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>51352</v>
+        <v>49910.3</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>25.3</v>
+        <v>24.59</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.2692307692307692</v>
+        <v>0.2538461538461538</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2029.723320158103</v>
+        <v>2029.699064660431</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.6769824087537935</v>
+        <v>0.6770509671385649</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03952569169960474</v>
+        <v>0.0406669377795852</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>73.07692307692308</v>
+        <v>74.61538461538461</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>81.15384615384616</v>
+        <v>82.23076923076923</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>29.58428571428571</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>60047.91462450592</v>
+        <v>60047.19704293267</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.169339356295878</v>
+        <v>0.2031023063963282</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>41.91</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>85065.70434782607</v>
+        <v>85064.68779991867</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.6565217391304345</v>
+        <v>0.7043513623424156</v>
       </c>
     </row>
     <row r="16">
@@ -4283,7 +4283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5100,6 +5100,39 @@
       </c>
       <c r="I24">
         <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B25" s="24" t="n">
+        <v>49910.3</v>
+      </c>
+      <c r="C25" s="25" t="n">
+        <v>24.59</v>
+      </c>
+      <c r="D25" s="26" t="n">
+        <v>0.253846153846</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>0.677050967139</v>
+      </c>
+      <c r="F25" s="34">
+        <f>IF(D25="","",100*(1-D25))</f>
+        <v/>
+      </c>
+      <c r="G25" s="34">
+        <f>IF(E25="","",IF(E25&lt;=0,20,IF(E25&lt;5%,20+400*E25,IF(E25&lt;10%,40+400*(E25-5%),IF(E25&lt;15%,60+400*(E25-10%),IF(E25&lt;25%,80+200*(E25-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H25" s="34">
+        <f>IF(OR(F25="",G25=""),"",70%*F25+30%*G25)</f>
+        <v/>
+      </c>
+      <c r="I25">
+        <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5140,7 +5173,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-22</t>
+          <t>Retrieved 2026-10-23</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-50.xlsx
+++ b/docs/downloads/indices/nifty-alpha-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>49910.3</v>
+        <v>51181.5</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>24.59</v>
+        <v>25.15</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.2538461538461538</v>
+        <v>0.2692307692307692</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2029.699064660431</v>
+        <v>2035.049701789264</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.6770509671385649</v>
+        <v>0.6814091866263534</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0406669377795852</v>
+        <v>0.03976143141153082</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>74.61538461538461</v>
+        <v>73.07692307692308</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>82.23076923076923</v>
+        <v>81.15384615384616</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>29.58428571428571</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>60047.19704293267</v>
+        <v>60205.49182050554</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.2031023063963282</v>
+        <v>0.1763135472877024</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>41.91</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>85064.68779991867</v>
+        <v>85288.93300198806</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.7043513623424156</v>
+        <v>0.6664015904572562</v>
       </c>
     </row>
     <row r="16">
@@ -4283,7 +4283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5133,6 +5133,39 @@
       </c>
       <c r="I25">
         <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B26" s="24" t="n">
+        <v>51181.5</v>
+      </c>
+      <c r="C26" s="25" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="D26" s="26" t="n">
+        <v>0.269230769231</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>0.681409186626</v>
+      </c>
+      <c r="F26" s="34">
+        <f>IF(D26="","",100*(1-D26))</f>
+        <v/>
+      </c>
+      <c r="G26" s="34">
+        <f>IF(E26="","",IF(E26&lt;=0,20,IF(E26&lt;5%,20+400*E26,IF(E26&lt;10%,40+400*(E26-5%),IF(E26&lt;15%,60+400*(E26-10%),IF(E26&lt;25%,80+200*(E26-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H26" s="34">
+        <f>IF(OR(F26="",G26=""),"",70%*F26+30%*G26)</f>
+        <v/>
+      </c>
+      <c r="I26">
+        <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5173,7 +5206,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-23</t>
+          <t>Retrieved 2026-10-26</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-50.xlsx
+++ b/docs/downloads/indices/nifty-alpha-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>51181.5</v>
+        <v>52426.75</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>25.15</v>
+        <v>25.01</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2035.049701789264</v>
+        <v>2096.231507397041</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.6814091866263534</v>
+        <v>0.7257181093374616</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03976143141153082</v>
+        <v>0.03998400639744102</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>29.58428571428571</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>60205.49182050554</v>
+        <v>62015.51183812189</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.1763135472877024</v>
+        <v>0.1828982692637231</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>41.91</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>85288.93300198806</v>
+        <v>87853.06247501</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.6664015904572562</v>
+        <v>0.6757297081167533</v>
       </c>
     </row>
     <row r="16">
@@ -4283,7 +4283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5166,6 +5166,39 @@
       </c>
       <c r="I26">
         <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B27" s="24" t="n">
+        <v>52426.75</v>
+      </c>
+      <c r="C27" s="25" t="n">
+        <v>25.01</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>0.269230769231</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>0.725718109337</v>
+      </c>
+      <c r="F27" s="34">
+        <f>IF(D27="","",100*(1-D27))</f>
+        <v/>
+      </c>
+      <c r="G27" s="34">
+        <f>IF(E27="","",IF(E27&lt;=0,20,IF(E27&lt;5%,20+400*E27,IF(E27&lt;10%,40+400*(E27-5%),IF(E27&lt;15%,60+400*(E27-10%),IF(E27&lt;25%,80+200*(E27-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H27" s="34">
+        <f>IF(OR(F27="",G27=""),"",70%*F27+30%*G27)</f>
+        <v/>
+      </c>
+      <c r="I27">
+        <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5206,7 +5239,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-26</t>
+          <t>Retrieved 2026-10-27</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-50.xlsx
+++ b/docs/downloads/indices/nifty-alpha-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>52426.75</v>
+        <v>52607.4</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>25.01</v>
+        <v>24.97</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2096.231507397041</v>
+        <v>2106.824189026832</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.7257181093374616</v>
+        <v>0.732737689841606</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.03998400639744102</v>
+        <v>0.04004805766920305</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>29.58428571428571</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>62015.51183812189</v>
+        <v>62328.8887579381</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.1828982692637231</v>
+        <v>0.1847931803878939</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>41.91</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>87853.06247501</v>
+        <v>88297.00176211454</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.6757297081167533</v>
+        <v>0.6784140969162995</v>
       </c>
     </row>
     <row r="16">
@@ -4283,7 +4283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5199,6 +5199,39 @@
       </c>
       <c r="I27">
         <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B28" s="24" t="n">
+        <v>52607.4</v>
+      </c>
+      <c r="C28" s="25" t="n">
+        <v>24.97</v>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>0.269230769231</v>
+      </c>
+      <c r="E28" s="26" t="n">
+        <v>0.7327376898420001</v>
+      </c>
+      <c r="F28" s="34">
+        <f>IF(D28="","",100*(1-D28))</f>
+        <v/>
+      </c>
+      <c r="G28" s="34">
+        <f>IF(E28="","",IF(E28&lt;=0,20,IF(E28&lt;5%,20+400*E28,IF(E28&lt;10%,40+400*(E28-5%),IF(E28&lt;15%,60+400*(E28-10%),IF(E28&lt;25%,80+200*(E28-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H28" s="34">
+        <f>IF(OR(F28="",G28=""),"",70%*F28+30%*G28)</f>
+        <v/>
+      </c>
+      <c r="I28">
+        <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5239,7 +5272,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-27</t>
+          <t>Retrieved 2026-10-28</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-50.xlsx
+++ b/docs/downloads/indices/nifty-alpha-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>52607.4</v>
+        <v>53204.45</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>24.97</v>
+        <v>25.26</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2106.824189026832</v>
+        <v>2106.272763262074</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.732737689841606</v>
+        <v>0.7309544786939639</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04004805766920305</v>
+        <v>0.0395882818685669</v>
       </c>
     </row>
     <row r="8">
@@ -739,10 +739,10 @@
         <v>29.58428571428571</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>62328.8887579381</v>
+        <v>62312.57522056327</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.1847931803878939</v>
+        <v>0.1711910417373597</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>41.91</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>88297.00176211454</v>
+        <v>88273.89150831352</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.6784140969162995</v>
+        <v>0.6591448931116388</v>
       </c>
     </row>
     <row r="16">
@@ -4283,7 +4283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5232,6 +5232,39 @@
       </c>
       <c r="I28">
         <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B29" s="24" t="n">
+        <v>53204.45</v>
+      </c>
+      <c r="C29" s="25" t="n">
+        <v>25.26</v>
+      </c>
+      <c r="D29" s="26" t="n">
+        <v>0.269230769231</v>
+      </c>
+      <c r="E29" s="26" t="n">
+        <v>0.730954478694</v>
+      </c>
+      <c r="F29" s="34">
+        <f>IF(D29="","",100*(1-D29))</f>
+        <v/>
+      </c>
+      <c r="G29" s="34">
+        <f>IF(E29="","",IF(E29&lt;=0,20,IF(E29&lt;5%,20+400*E29,IF(E29&lt;10%,40+400*(E29-5%),IF(E29&lt;15%,60+400*(E29-10%),IF(E29&lt;25%,80+200*(E29-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H29" s="34">
+        <f>IF(OR(F29="",G29=""),"",70%*F29+30%*G29)</f>
+        <v/>
+      </c>
+      <c r="I29">
+        <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5272,7 +5305,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-28</t>
+          <t>Retrieved 2026-10-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">

--- a/docs/downloads/indices/nifty-alpha-50.xlsx
+++ b/docs/downloads/indices/nifty-alpha-50.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>53204.45</v>
+        <v>52498.6</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>25.26</v>
+        <v>24.36</v>
       </c>
     </row>
     <row r="6">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.2692307692307692</v>
+        <v>0.2461538461538462</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>2106.272763262074</v>
+        <v>2155.114942528736</v>
       </c>
     </row>
     <row r="7">
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.7309544786939639</v>
+        <v>0.7664307355999267</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0395882818685669</v>
+        <v>0.04105090311986864</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>73.07692307692308</v>
+        <v>75.38461538461539</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>81.15384615384616</v>
+        <v>82.76923076923077</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -739,10 +739,10 @@
         <v>29.58428571428571</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>62312.57522056327</v>
+        <v>63757.53620689656</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.1711910417373597</v>
+        <v>0.2144616467276568</v>
       </c>
     </row>
     <row r="14">
@@ -755,10 +755,10 @@
         <v>41.91</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>88273.89150831352</v>
+        <v>90320.86724137931</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.6591448931116388</v>
+        <v>0.7204433497536946</v>
       </c>
     </row>
     <row r="16">
@@ -4283,7 +4283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5265,6 +5265,39 @@
       </c>
       <c r="I29">
         <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B30" s="24" t="n">
+        <v>52498.6</v>
+      </c>
+      <c r="C30" s="25" t="n">
+        <v>24.36</v>
+      </c>
+      <c r="D30" s="26" t="n">
+        <v>0.246153846154</v>
+      </c>
+      <c r="E30" s="26" t="n">
+        <v>0.7664307356</v>
+      </c>
+      <c r="F30" s="34">
+        <f>IF(D30="","",100*(1-D30))</f>
+        <v/>
+      </c>
+      <c r="G30" s="34">
+        <f>IF(E30="","",IF(E30&lt;=0,20,IF(E30&lt;5%,20+400*E30,IF(E30&lt;10%,40+400*(E30-5%),IF(E30&lt;15%,60+400*(E30-10%),IF(E30&lt;25%,80+200*(E30-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H30" s="34">
+        <f>IF(OR(F30="",G30=""),"",70%*F30+30%*G30)</f>
+        <v/>
+      </c>
+      <c r="I30">
+        <f>IF(H30="","",IF(H30&gt;=70,"BUY",IF(H30&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5305,7 +5338,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Retrieved 2026-10-29</t>
+          <t>Retrieved 2026-10-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
